--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F36AF66-4FB3-4A2E-A02B-6B5BF3231B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE141200-8C11-4F4D-B36D-653ABAFC92CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1195,7 +1195,9 @@
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="8">
+        <v>46281</v>
+      </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE141200-8C11-4F4D-B36D-653ABAFC92CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3E83E4-ED79-4981-9017-75A946D5BC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Body is so weak in today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stressful day </t>
   </si>
 </sst>
 </file>
@@ -379,7 +382,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -858,14 +863,14 @@
     <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" customWidth="1"/>
+    <col min="10" max="10" width="19.88671875" customWidth="1"/>
     <col min="11" max="11" width="8.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -938,7 +943,7 @@
       <c r="M4" s="13"/>
       <c r="N4" s="13"/>
     </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1168,7 +1173,7 @@
         <v>480</v>
       </c>
       <c r="C10" s="9">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
@@ -1177,11 +1182,11 @@
       <c r="H10" s="9"/>
       <c r="I10" s="10">
         <f t="shared" si="2"/>
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="3"/>
-        <v>950</v>
+        <v>920</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>56</v>
@@ -1196,44 +1201,64 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46281</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+        <v>46265</v>
+      </c>
+      <c r="B11" s="9">
+        <v>380</v>
+      </c>
+      <c r="C11" s="9">
+        <v>80</v>
+      </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
+      <c r="F11" s="9">
+        <v>350</v>
+      </c>
+      <c r="G11" s="9">
+        <v>7</v>
+      </c>
       <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
+      <c r="I11" s="10">
+        <f t="shared" si="2"/>
+        <v>810</v>
+      </c>
+      <c r="J11" s="10">
+        <f t="shared" si="3"/>
+        <v>630</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>56</v>
+      </c>
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="A12" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B12" s="9">
+        <v>420</v>
+      </c>
+      <c r="C12" s="9">
+        <v>70</v>
+      </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
+      <c r="F12" s="9">
+        <v>250</v>
+      </c>
+      <c r="G12" s="9">
+        <v>5</v>
+      </c>
       <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I12" s="10">
+        <f t="shared" si="2"/>
+        <v>740</v>
+      </c>
+      <c r="J12" s="10">
+        <f t="shared" si="3"/>
+        <v>700</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -1241,21 +1266,31 @@
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="A13" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B13" s="9">
+        <v>330</v>
+      </c>
+      <c r="C13" s="9">
+        <v>80</v>
+      </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
+      <c r="F13" s="9">
+        <v>200</v>
+      </c>
+      <c r="G13" s="9">
+        <v>4</v>
+      </c>
       <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I13" s="10">
+        <f t="shared" si="2"/>
+        <v>610</v>
+      </c>
+      <c r="J13" s="10">
+        <f t="shared" si="3"/>
+        <v>830</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1263,21 +1298,31 @@
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="A14" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B14" s="9">
+        <v>330</v>
+      </c>
+      <c r="C14" s="9">
+        <v>80</v>
+      </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
+      <c r="F14" s="9">
+        <v>250</v>
+      </c>
+      <c r="G14" s="9">
+        <v>5</v>
+      </c>
       <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I14" s="10">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J14" s="10">
+        <f t="shared" si="3"/>
+        <v>780</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -1285,21 +1330,31 @@
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="A15" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="9">
+        <v>340</v>
+      </c>
+      <c r="C15" s="9">
+        <v>80</v>
+      </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="F15" s="9">
+        <v>300</v>
+      </c>
+      <c r="G15" s="9">
+        <v>6</v>
+      </c>
       <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I15" s="10">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="3"/>
+        <v>720</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -1307,21 +1362,27 @@
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="A16" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B16" s="9">
+        <v>420</v>
+      </c>
+      <c r="C16" s="9">
+        <v>80</v>
+      </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I16" s="10">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="3"/>
+        <v>940</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -1329,21 +1390,27 @@
       <c r="N16" s="12"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="A17" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B17" s="9">
+        <v>440</v>
+      </c>
+      <c r="C17" s="9">
+        <v>80</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I17" s="10">
+        <f t="shared" si="2"/>
+        <v>520</v>
+      </c>
+      <c r="J17" s="10">
+        <f t="shared" si="3"/>
+        <v>920</v>
       </c>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -1351,21 +1418,31 @@
       <c r="N17" s="12"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="A18" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B18" s="9">
+        <v>410</v>
+      </c>
+      <c r="C18" s="9">
+        <v>80</v>
+      </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="9">
+        <v>350</v>
+      </c>
+      <c r="G18" s="9">
+        <v>7</v>
+      </c>
       <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I18" s="10">
+        <f>IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <v>840</v>
+      </c>
+      <c r="J18" s="10">
+        <f t="shared" si="3"/>
+        <v>600</v>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -1373,21 +1450,31 @@
       <c r="N18" s="12"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
+      <c r="A19" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B19" s="9">
+        <v>340</v>
+      </c>
+      <c r="C19" s="9">
+        <v>80</v>
+      </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="F19" s="9">
+        <v>250</v>
+      </c>
+      <c r="G19" s="9">
+        <v>5</v>
+      </c>
       <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I19" s="10">
+        <f t="shared" si="2"/>
+        <v>670</v>
+      </c>
+      <c r="J19" s="10">
+        <f t="shared" si="3"/>
+        <v>770</v>
       </c>
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
@@ -1395,21 +1482,31 @@
       <c r="N19" s="12"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
+      <c r="A20" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B20" s="9">
+        <v>340</v>
+      </c>
+      <c r="C20" s="9">
+        <v>80</v>
+      </c>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="9">
+        <v>200</v>
+      </c>
+      <c r="G20" s="9">
+        <v>4</v>
+      </c>
       <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I20" s="10">
+        <f t="shared" si="2"/>
+        <v>620</v>
+      </c>
+      <c r="J20" s="10">
+        <f t="shared" si="3"/>
+        <v>820</v>
       </c>
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
@@ -1417,21 +1514,31 @@
       <c r="N20" s="12"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
+      <c r="A21" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B21" s="9">
+        <v>360</v>
+      </c>
+      <c r="C21" s="9">
+        <v>80</v>
+      </c>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="F21" s="9">
+        <v>250</v>
+      </c>
+      <c r="G21" s="9">
+        <v>5</v>
+      </c>
       <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I21" s="10">
+        <f t="shared" si="2"/>
+        <v>690</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="3"/>
+        <v>750</v>
       </c>
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
@@ -1439,21 +1546,31 @@
       <c r="N21" s="12"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
+      <c r="A22" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B22" s="9">
+        <v>280</v>
+      </c>
+      <c r="C22" s="9">
+        <v>80</v>
+      </c>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="9">
+        <v>300</v>
+      </c>
+      <c r="G22" s="9">
+        <v>6</v>
+      </c>
       <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I22" s="10">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="3"/>
+        <v>780</v>
       </c>
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
@@ -1461,21 +1578,31 @@
       <c r="N22" s="12"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
+      <c r="A23" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B23" s="9">
+        <v>380</v>
+      </c>
+      <c r="C23" s="9">
+        <v>80</v>
+      </c>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
       <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I23" s="10">
+        <f t="shared" si="2"/>
+        <v>460</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="3"/>
+        <v>980</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
@@ -1483,21 +1610,31 @@
       <c r="N23" s="12"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
+      <c r="A24" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B24" s="9">
+        <v>390</v>
+      </c>
+      <c r="C24" s="9">
+        <v>180</v>
+      </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
       <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I24" s="10">
+        <f t="shared" si="2"/>
+        <v>570</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="3"/>
+        <v>870</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
@@ -1505,21 +1642,31 @@
       <c r="N24" s="12"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
+      <c r="A25" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B25" s="9">
+        <v>350</v>
+      </c>
+      <c r="C25" s="9">
+        <v>80</v>
+      </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="F25" s="9">
+        <v>350</v>
+      </c>
+      <c r="G25" s="9">
+        <v>7</v>
+      </c>
       <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I25" s="10">
+        <f t="shared" si="2"/>
+        <v>780</v>
+      </c>
+      <c r="J25" s="10">
+        <f t="shared" si="3"/>
+        <v>660</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
@@ -1527,21 +1674,31 @@
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
+      <c r="A26" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B26" s="9">
+        <v>360</v>
+      </c>
+      <c r="C26" s="9">
+        <v>80</v>
+      </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="F26" s="9">
+        <v>250</v>
+      </c>
+      <c r="G26" s="9">
+        <v>5</v>
+      </c>
       <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I26" s="10">
+        <f t="shared" si="2"/>
+        <v>690</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="3"/>
+        <v>750</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -1549,21 +1706,31 @@
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
+      <c r="A27" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B27" s="9">
+        <v>320</v>
+      </c>
+      <c r="C27" s="9">
+        <v>80</v>
+      </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="F27" s="9">
+        <v>250</v>
+      </c>
+      <c r="G27" s="9">
+        <v>5</v>
+      </c>
       <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I27" s="10">
+        <f t="shared" si="2"/>
+        <v>650</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="3"/>
+        <v>790</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -1571,21 +1738,31 @@
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
+      <c r="A28" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B28" s="9">
+        <v>320</v>
+      </c>
+      <c r="C28" s="9">
+        <v>80</v>
+      </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="9">
+        <v>250</v>
+      </c>
+      <c r="G28" s="9">
+        <v>5</v>
+      </c>
       <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I28" s="10">
+        <f t="shared" si="2"/>
+        <v>650</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" si="3"/>
+        <v>790</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -1593,21 +1770,27 @@
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
+      <c r="A29" s="8">
+        <v>46283</v>
+      </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="F29" s="9">
+        <v>300</v>
+      </c>
+      <c r="G29" s="9">
+        <v>6</v>
+      </c>
       <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I29" s="10">
+        <f t="shared" si="2"/>
+        <v>300</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="3"/>
+        <v>1140</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -1615,43 +1798,73 @@
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+      <c r="A30" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B30" s="9">
+        <v>300</v>
+      </c>
+      <c r="C30" s="9">
+        <v>60</v>
+      </c>
+      <c r="D30" s="9">
+        <v>120</v>
+      </c>
+      <c r="E30" s="9">
+        <v>40</v>
+      </c>
+      <c r="F30" s="9">
+        <v>60</v>
+      </c>
+      <c r="G30" s="9">
+        <v>1</v>
+      </c>
+      <c r="H30" s="9">
+        <v>150</v>
+      </c>
+      <c r="I30" s="10">
+        <f t="shared" si="2"/>
+        <v>730</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" si="3"/>
+        <v>710</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
+      <c r="A31" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B31" s="9">
+        <v>540</v>
+      </c>
+      <c r="C31" s="9">
+        <v>10</v>
+      </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I31" s="10">
+        <f t="shared" si="2"/>
+        <v>550</v>
+      </c>
+      <c r="J31" s="10">
+        <f t="shared" si="3"/>
+        <v>890</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="11"/>
@@ -1659,7 +1872,9 @@
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
+      <c r="A32" s="8">
+        <v>46286</v>
+      </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -1681,7 +1896,9 @@
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
+      <c r="A33" s="8">
+        <v>46287</v>
+      </c>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -1703,7 +1920,9 @@
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
+      <c r="A34" s="8">
+        <v>46288</v>
+      </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -1725,7 +1944,9 @@
       <c r="N34" s="12"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
+      <c r="A35" s="8">
+        <v>46289</v>
+      </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -1747,7 +1968,9 @@
       <c r="N35" s="12"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
+      <c r="A36" s="8">
+        <v>46290</v>
+      </c>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -1769,7 +1992,9 @@
       <c r="N36" s="12"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
+      <c r="A37" s="8">
+        <v>46291</v>
+      </c>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -1791,7 +2016,9 @@
       <c r="N37" s="12"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
+      <c r="A38" s="8">
+        <v>46292</v>
+      </c>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -1813,7 +2040,9 @@
       <c r="N38" s="12"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
+      <c r="A39" s="8">
+        <v>46293</v>
+      </c>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -1835,7 +2064,9 @@
       <c r="N39" s="12"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
+      <c r="A40" s="8">
+        <v>46294</v>
+      </c>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3E83E4-ED79-4981-9017-75A946D5BC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D7736A-2784-42A7-A3ED-9400896DFA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t xml:space="preserve">Stressful day </t>
+  </si>
+  <si>
+    <t>Weekend</t>
   </si>
 </sst>
 </file>
@@ -1853,23 +1856,41 @@
       <c r="C31" s="9">
         <v>10</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
+      <c r="D31" s="9">
+        <v>180</v>
+      </c>
+      <c r="E31" s="9">
+        <v>30</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
+        <v>120</v>
+      </c>
       <c r="I31" s="10">
         <f t="shared" si="2"/>
-        <v>550</v>
+        <v>880</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="3"/>
-        <v>890</v>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>560</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8">

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D7736A-2784-42A7-A3ED-9400896DFA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A91AEE4-54AF-4110-93AA-1AD1DBE813F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1896,24 +1896,44 @@
       <c r="A32" s="8">
         <v>46286</v>
       </c>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
+      <c r="B32" s="9">
+        <v>360</v>
+      </c>
+      <c r="C32" s="9">
+        <v>70</v>
+      </c>
+      <c r="D32" s="9">
+        <v>240</v>
+      </c>
+      <c r="E32" s="9">
+        <v>80</v>
+      </c>
+      <c r="F32" s="9">
+        <v>350</v>
+      </c>
+      <c r="G32" s="9">
+        <v>7</v>
+      </c>
+      <c r="H32" s="9">
+        <v>30</v>
+      </c>
+      <c r="I32" s="10">
+        <f t="shared" si="2"/>
+        <v>1130</v>
+      </c>
+      <c r="J32" s="10">
+        <f t="shared" si="3"/>
+        <v>310</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A91AEE4-54AF-4110-93AA-1AD1DBE813F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AA6670-B41E-4D9B-8B0E-092116E45BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,18 @@
   </si>
   <si>
     <t>Weekend</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>A day in the mountains, finding peace away from the noise of life.</t>
+  </si>
+  <si>
+    <t>Back to my room, carrying memories of a beautiful day in the mountains.</t>
   </si>
 </sst>
 </file>
@@ -866,14 +878,14 @@
     <col min="4" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="16.21875" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" customWidth="1"/>
-    <col min="11" max="11" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="63.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1580,69 +1592,97 @@
       <c r="M22" s="11"/>
       <c r="N22" s="12"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>46277</v>
       </c>
       <c r="B23" s="9">
-        <v>380</v>
+        <v>120</v>
       </c>
       <c r="C23" s="9">
-        <v>80</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+        <v>210</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
       <c r="F23" s="9">
         <v>0</v>
       </c>
       <c r="G23" s="9">
         <v>0</v>
       </c>
-      <c r="H23" s="9"/>
+      <c r="H23" s="9">
+        <v>150</v>
+      </c>
       <c r="I23" s="10">
         <f t="shared" si="2"/>
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="J23" s="10">
         <f t="shared" si="3"/>
-        <v>980</v>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+        <v>960</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>46278</v>
       </c>
       <c r="B24" s="9">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="C24" s="9">
-        <v>180</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+        <v>150</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0</v>
+      </c>
       <c r="F24" s="9">
         <v>0</v>
       </c>
       <c r="G24" s="9">
         <v>0</v>
       </c>
-      <c r="H24" s="9"/>
+      <c r="H24" s="9">
+        <v>90</v>
+      </c>
       <c r="I24" s="10">
         <f t="shared" si="2"/>
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="3"/>
-        <v>870</v>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>920</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8">

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AA6670-B41E-4D9B-8B0E-092116E45BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6DB79D-AC5A-4920-B140-D671C00F8A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -208,9 +208,6 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>I have decided to stay consistent and focus on my studies</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -220,9 +217,6 @@
     <t>Unsatisfied</t>
   </si>
   <si>
-    <t>Body is so weak in today</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stressful day </t>
   </si>
   <si>
@@ -239,6 +233,27 @@
   </si>
   <si>
     <t>Back to my room, carrying memories of a beautiful day in the mountains.</t>
+  </si>
+  <si>
+    <t>When I saw the communication skills results, I was dissapointed because I expected more than that</t>
+  </si>
+  <si>
+    <t>Started the day following a consistent routine.</t>
+  </si>
+  <si>
+    <t>Focused on academic tasks and keeping up with classes.</t>
+  </si>
+  <si>
+    <t>Weekend relaxation and recovery.</t>
+  </si>
+  <si>
+    <t>Enjoyed a peaceful weekend day.</t>
+  </si>
+  <si>
+    <t>Back to the regular weekday schedule and focused studies.</t>
+  </si>
+  <si>
+    <t>Ready for the weekend to get here</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1017,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46260</v>
       </c>
@@ -1045,7 +1060,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1070,14 +1085,16 @@
       <c r="G7" s="9">
         <v>5</v>
       </c>
-      <c r="H7" s="9"/>
+      <c r="H7" s="9">
+        <v>20</v>
+      </c>
       <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>49</v>
@@ -1088,7 +1105,9 @@
       <c r="M7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="12"/>
+      <c r="N7" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
@@ -1130,9 +1149,11 @@
         <v>50</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="12"/>
+        <v>58</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
@@ -1168,16 +1189,16 @@
         <v>730</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1190,18 +1211,28 @@
       <c r="C10" s="9">
         <v>40</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="D10" s="9">
+        <v>240</v>
+      </c>
+      <c r="E10" s="9">
+        <v>30</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>10</v>
+      </c>
       <c r="I10" s="10">
         <f t="shared" si="2"/>
-        <v>520</v>
+        <v>800</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="3"/>
-        <v>920</v>
+        <v>640</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>56</v>
@@ -1212,7 +1243,9 @@
       <c r="M10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="12"/>
+      <c r="N10" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
@@ -1224,29 +1257,41 @@
       <c r="C11" s="9">
         <v>80</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="9">
+        <v>150</v>
+      </c>
+      <c r="E11" s="9">
+        <v>45</v>
+      </c>
       <c r="F11" s="9">
         <v>350</v>
       </c>
       <c r="G11" s="9">
         <v>7</v>
       </c>
-      <c r="H11" s="9"/>
+      <c r="H11" s="9">
+        <v>60</v>
+      </c>
       <c r="I11" s="10">
         <f t="shared" si="2"/>
-        <v>810</v>
+        <v>1065</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="3"/>
-        <v>630</v>
+        <v>375</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
+      <c r="L11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
@@ -1388,8 +1433,12 @@
       </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
       <c r="H16" s="9"/>
       <c r="I16" s="10">
         <f t="shared" si="2"/>
@@ -1416,8 +1465,12 @@
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
       <c r="H17" s="9"/>
       <c r="I17" s="10">
         <f t="shared" si="2"/>
@@ -1626,16 +1679,16 @@
         <v>960</v>
       </c>
       <c r="K23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1681,7 +1734,7 @@
         <v>51</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1877,13 +1930,13 @@
         <v>56</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M30" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -1929,7 +1982,7 @@
         <v>51</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1976,29 +2029,51 @@
       </c>
       <c r="N32" s="12"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46287</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+      <c r="B33" s="9">
+        <v>420</v>
+      </c>
+      <c r="C33" s="9">
+        <v>80</v>
+      </c>
+      <c r="D33" s="9">
+        <v>180</v>
+      </c>
+      <c r="E33" s="9">
+        <v>30</v>
+      </c>
+      <c r="F33" s="9">
+        <v>250</v>
+      </c>
+      <c r="G33" s="9">
+        <v>5</v>
+      </c>
+      <c r="H33" s="9">
+        <v>20</v>
+      </c>
+      <c r="I33" s="10">
+        <f t="shared" si="2"/>
+        <v>980</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="3"/>
+        <v>460</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
@@ -4542,7 +4617,6 @@
       <c r="K148" s="11"/>
       <c r="L148" s="11"/>
       <c r="M148" s="11"/>
-      <c r="N148" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED6DB79D-AC5A-4920-B140-D671C00F8A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A11A9E4-EDE1-4556-8B6D-D15F550CB1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>Ready for the weekend to get here</t>
+  </si>
+  <si>
+    <t>I have a CA tomorrow, but I’m not feeling well, so I’m unable to study for it.</t>
   </si>
 </sst>
 </file>
@@ -884,7 +887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -1019,306 +1022,166 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46260</v>
-      </c>
-      <c r="B6" s="9">
-        <v>270</v>
-      </c>
-      <c r="C6" s="9">
-        <v>80</v>
-      </c>
-      <c r="D6" s="9">
-        <v>210</v>
-      </c>
-      <c r="E6" s="9">
-        <v>20</v>
-      </c>
-      <c r="F6" s="9">
-        <v>200</v>
-      </c>
-      <c r="G6" s="9">
-        <v>4</v>
-      </c>
-      <c r="H6" s="9">
-        <v>30</v>
-      </c>
-      <c r="I6" s="10">
-        <f t="shared" ref="I6:I8" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>810</v>
-      </c>
-      <c r="J6" s="10">
-        <f t="shared" ref="J6:J8" si="1">IF(I6="","",1440-I6)</f>
-        <v>630</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>67</v>
-      </c>
+        <v>46247</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10" t="str">
+        <f t="shared" ref="I6:I13" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v/>
+      </c>
+      <c r="J6" s="10" t="str">
+        <f t="shared" ref="J6:J13" si="1">IF(I6="","",1440-I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46261</v>
-      </c>
-      <c r="B7" s="9">
-        <v>300</v>
-      </c>
-      <c r="C7" s="9">
-        <v>70</v>
-      </c>
-      <c r="D7" s="9">
-        <v>180</v>
-      </c>
-      <c r="E7" s="9">
-        <v>30</v>
-      </c>
-      <c r="F7" s="9">
-        <v>250</v>
-      </c>
-      <c r="G7" s="9">
-        <v>5</v>
-      </c>
-      <c r="H7" s="9">
-        <v>20</v>
-      </c>
-      <c r="I7" s="10">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-      <c r="J7" s="10">
+        <v/>
+      </c>
+      <c r="J7" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>590</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>68</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46262</v>
-      </c>
-      <c r="B8" s="9">
-        <v>360</v>
-      </c>
-      <c r="C8" s="9">
-        <v>80</v>
-      </c>
-      <c r="D8" s="9">
-        <v>200</v>
-      </c>
-      <c r="E8" s="9">
-        <v>30</v>
-      </c>
-      <c r="F8" s="9">
-        <v>300</v>
-      </c>
-      <c r="G8" s="9">
-        <v>6</v>
-      </c>
-      <c r="H8" s="9">
-        <v>120</v>
-      </c>
-      <c r="I8" s="10">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>1090</v>
-      </c>
-      <c r="J8" s="10">
+        <v/>
+      </c>
+      <c r="J8" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>350</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>72</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46263</v>
-      </c>
-      <c r="B9" s="9">
-        <v>360</v>
-      </c>
-      <c r="C9" s="9">
-        <v>20</v>
-      </c>
-      <c r="D9" s="9">
-        <v>260</v>
-      </c>
-      <c r="E9" s="9">
-        <v>40</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>30</v>
-      </c>
-      <c r="I9" s="10">
-        <f t="shared" ref="I9:I72" si="2">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v>710</v>
-      </c>
-      <c r="J9" s="10">
-        <f t="shared" ref="J9:J72" si="3">IF(I9="","",1440-I9)</f>
-        <v>730</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>69</v>
-      </c>
+        <v>46250</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J9" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46264</v>
-      </c>
-      <c r="B10" s="9">
-        <v>480</v>
-      </c>
-      <c r="C10" s="9">
-        <v>40</v>
-      </c>
-      <c r="D10" s="9">
-        <v>240</v>
-      </c>
-      <c r="E10" s="9">
-        <v>30</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>10</v>
-      </c>
-      <c r="I10" s="10">
-        <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="J10" s="10">
-        <f t="shared" si="3"/>
-        <v>640</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>70</v>
-      </c>
+        <v>46251</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J10" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46265</v>
-      </c>
-      <c r="B11" s="9">
-        <v>380</v>
-      </c>
-      <c r="C11" s="9">
-        <v>80</v>
-      </c>
-      <c r="D11" s="9">
-        <v>150</v>
-      </c>
-      <c r="E11" s="9">
-        <v>45</v>
-      </c>
-      <c r="F11" s="9">
-        <v>350</v>
-      </c>
-      <c r="G11" s="9">
-        <v>7</v>
-      </c>
-      <c r="H11" s="9">
-        <v>60</v>
-      </c>
-      <c r="I11" s="10">
-        <f t="shared" si="2"/>
-        <v>1065</v>
-      </c>
-      <c r="J11" s="10">
-        <f t="shared" si="3"/>
-        <v>375</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="12" t="s">
-        <v>71</v>
-      </c>
+        <v>46252</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J11" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46266</v>
-      </c>
-      <c r="B12" s="9">
-        <v>420</v>
-      </c>
-      <c r="C12" s="9">
-        <v>70</v>
-      </c>
+        <v>46253</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="9">
-        <v>250</v>
-      </c>
-      <c r="G12" s="9">
-        <v>5</v>
-      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="10">
-        <f t="shared" si="2"/>
-        <v>740</v>
-      </c>
-      <c r="J12" s="10">
-        <f t="shared" si="3"/>
-        <v>700</v>
+      <c r="I12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J12" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -1327,30 +1190,22 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46267</v>
-      </c>
-      <c r="B13" s="9">
-        <v>330</v>
-      </c>
-      <c r="C13" s="9">
-        <v>80</v>
-      </c>
+        <v>46254</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
-      <c r="F13" s="9">
-        <v>200</v>
-      </c>
-      <c r="G13" s="9">
-        <v>4</v>
-      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="10">
-        <f t="shared" si="2"/>
-        <v>610</v>
-      </c>
-      <c r="J13" s="10">
-        <f t="shared" si="3"/>
-        <v>830</v>
+      <c r="I13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J13" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1359,30 +1214,22 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46268</v>
-      </c>
-      <c r="B14" s="9">
-        <v>330</v>
-      </c>
-      <c r="C14" s="9">
-        <v>80</v>
-      </c>
+        <v>46255</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="F14" s="9">
-        <v>250</v>
-      </c>
-      <c r="G14" s="9">
-        <v>5</v>
-      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="10">
-        <f t="shared" si="2"/>
-        <v>660</v>
-      </c>
-      <c r="J14" s="10">
-        <f t="shared" si="3"/>
-        <v>780</v>
+      <c r="I14" s="10" t="str">
+        <f t="shared" ref="I14:I18" si="2">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
+        <v/>
+      </c>
+      <c r="J14" s="10" t="str">
+        <f t="shared" ref="J14:J18" si="3">IF(I14="","",1440-I14)</f>
+        <v/>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -1391,30 +1238,22 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46269</v>
-      </c>
-      <c r="B15" s="9">
-        <v>340</v>
-      </c>
-      <c r="C15" s="9">
-        <v>80</v>
-      </c>
+        <v>46256</v>
+      </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
-      <c r="F15" s="9">
-        <v>300</v>
-      </c>
-      <c r="G15" s="9">
-        <v>6</v>
-      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="10">
+      <c r="I15" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>720</v>
-      </c>
-      <c r="J15" s="10">
+        <v/>
+      </c>
+      <c r="J15" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>720</v>
+        <v/>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -1423,30 +1262,22 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B16" s="9">
-        <v>420</v>
-      </c>
-      <c r="C16" s="9">
-        <v>80</v>
-      </c>
+        <v>46257</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="10">
+      <c r="I16" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>500</v>
-      </c>
-      <c r="J16" s="10">
+        <v/>
+      </c>
+      <c r="J16" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>940</v>
+        <v/>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -1455,30 +1286,22 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46271</v>
-      </c>
-      <c r="B17" s="9">
-        <v>440</v>
-      </c>
-      <c r="C17" s="9">
-        <v>80</v>
-      </c>
+        <v>46258</v>
+      </c>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
-      <c r="F17" s="9">
-        <v>0</v>
-      </c>
-      <c r="G17" s="9">
-        <v>0</v>
-      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="10">
+      <c r="I17" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>520</v>
-      </c>
-      <c r="J17" s="10">
+        <v/>
+      </c>
+      <c r="J17" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>920</v>
+        <v/>
       </c>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -1487,30 +1310,22 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46272</v>
-      </c>
-      <c r="B18" s="9">
-        <v>410</v>
-      </c>
-      <c r="C18" s="9">
-        <v>80</v>
-      </c>
+        <v>46259</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="9">
-        <v>350</v>
-      </c>
-      <c r="G18" s="9">
-        <v>7</v>
-      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="10">
-        <f>IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
-        <v>840</v>
-      </c>
-      <c r="J18" s="10">
+      <c r="I18" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J18" s="10" t="str">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v/>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -1519,71 +1334,99 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46273</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="9">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="C19" s="9">
         <v>80</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="D19" s="9">
+        <v>210</v>
+      </c>
+      <c r="E19" s="9">
+        <v>20</v>
+      </c>
       <c r="F19" s="9">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="G19" s="9">
-        <v>5</v>
-      </c>
-      <c r="H19" s="9"/>
+        <v>4</v>
+      </c>
+      <c r="H19" s="9">
+        <v>30</v>
+      </c>
       <c r="I19" s="10">
-        <f t="shared" si="2"/>
-        <v>670</v>
+        <f t="shared" ref="I19:I21" si="4">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <v>810</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="3"/>
-        <v>770</v>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <f t="shared" ref="J19:J21" si="5">IF(I19="","",1440-I19)</f>
+        <v>630</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46274</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="9">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="C20" s="9">
-        <v>80</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="D20" s="9">
+        <v>180</v>
+      </c>
+      <c r="E20" s="9">
+        <v>30</v>
+      </c>
       <c r="F20" s="9">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G20" s="9">
-        <v>4</v>
-      </c>
-      <c r="H20" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="H20" s="9">
+        <v>20</v>
+      </c>
       <c r="I20" s="10">
-        <f t="shared" si="2"/>
-        <v>620</v>
+        <f t="shared" si="4"/>
+        <v>850</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="3"/>
-        <v>820</v>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+        <f t="shared" si="5"/>
+        <v>590</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46275</v>
+        <v>46262</v>
       </c>
       <c r="B21" s="9">
         <v>360</v>
@@ -1591,75 +1434,103 @@
       <c r="C21" s="9">
         <v>80</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="9">
+        <v>200</v>
+      </c>
+      <c r="E21" s="9">
+        <v>30</v>
+      </c>
       <c r="F21" s="9">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G21" s="9">
-        <v>5</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="H21" s="9">
+        <v>120</v>
+      </c>
       <c r="I21" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
+        <f t="shared" si="4"/>
+        <v>1090</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <f t="shared" si="5"/>
+        <v>350</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>46276</v>
+        <v>46263</v>
       </c>
       <c r="B22" s="9">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="C22" s="9">
-        <v>80</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="D22" s="9">
+        <v>260</v>
+      </c>
+      <c r="E22" s="9">
+        <v>40</v>
+      </c>
       <c r="F22" s="9">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G22" s="9">
-        <v>6</v>
-      </c>
-      <c r="H22" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>30</v>
+      </c>
       <c r="I22" s="10">
-        <f t="shared" si="2"/>
-        <v>660</v>
+        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>710</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="3"/>
-        <v>780</v>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+        <f>IF(I22="","",1440-I22)</f>
+        <v>730</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
-        <v>46277</v>
+        <v>46264</v>
       </c>
       <c r="B23" s="9">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="C23" s="9">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="D23" s="9">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="E23" s="9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
@@ -1668,101 +1539,101 @@
         <v>0</v>
       </c>
       <c r="H23" s="9">
+        <v>10</v>
+      </c>
+      <c r="I23" s="10">
+        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <v>800</v>
+      </c>
+      <c r="J23" s="10">
+        <f>IF(I23="","",1440-I23)</f>
+        <v>640</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="9">
+        <v>380</v>
+      </c>
+      <c r="C24" s="9">
+        <v>80</v>
+      </c>
+      <c r="D24" s="9">
         <v>150</v>
       </c>
-      <c r="I23" s="10">
-        <f t="shared" si="2"/>
-        <v>480</v>
-      </c>
-      <c r="J23" s="10">
-        <f t="shared" si="3"/>
-        <v>960</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="M23" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
-        <v>46278</v>
-      </c>
-      <c r="B24" s="9">
-        <v>280</v>
-      </c>
-      <c r="C24" s="9">
-        <v>150</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
       <c r="E24" s="9">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F24" s="9">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="G24" s="9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H24" s="9">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="2"/>
-        <v>520</v>
+        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <v>1065</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="3"/>
-        <v>920</v>
+        <f>IF(I24="","",1440-I24)</f>
+        <v>375</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M24" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="B25" s="9">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="C25" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G25" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="10">
-        <f t="shared" si="2"/>
-        <v>780</v>
+        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <v>740</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="3"/>
-        <v>660</v>
+        <f>IF(I25="","",1440-I25)</f>
+        <v>700</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
@@ -1771,10 +1642,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
-        <v>46280</v>
+        <v>46269</v>
       </c>
       <c r="B26" s="9">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C26" s="9">
         <v>80</v>
@@ -1782,19 +1653,19 @@
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="G26" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="10">
-        <f t="shared" si="2"/>
-        <v>690</v>
+        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <v>720</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="3"/>
-        <v>750</v>
+        <f>IF(I26="","",1440-I26)</f>
+        <v>720</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
@@ -1803,10 +1674,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
-        <v>46281</v>
+        <v>46270</v>
       </c>
       <c r="B27" s="9">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="C27" s="9">
         <v>80</v>
@@ -1814,19 +1685,19 @@
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G27" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="10">
-        <f t="shared" si="2"/>
-        <v>650</v>
+        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <v>500</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="3"/>
-        <v>790</v>
+        <f>IF(I27="","",1440-I27)</f>
+        <v>940</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
@@ -1835,10 +1706,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46282</v>
+        <v>46271</v>
       </c>
       <c r="B28" s="9">
-        <v>320</v>
+        <v>440</v>
       </c>
       <c r="C28" s="9">
         <v>80</v>
@@ -1846,19 +1717,19 @@
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G28" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="10">
-        <f t="shared" si="2"/>
-        <v>650</v>
+        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <v>520</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="3"/>
-        <v>790</v>
+        <f>IF(I28="","",1440-I28)</f>
+        <v>920</v>
       </c>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -1867,26 +1738,30 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
-        <v>46283</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
+        <v>46272</v>
+      </c>
+      <c r="B29" s="9">
+        <v>410</v>
+      </c>
+      <c r="C29" s="9">
+        <v>80</v>
+      </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G29" s="9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="10">
-        <f t="shared" si="2"/>
-        <v>300</v>
+        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <v>840</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="3"/>
-        <v>1140</v>
+        <f>IF(I29="","",1440-I29)</f>
+        <v>600</v>
       </c>
       <c r="K29" s="11"/>
       <c r="L29" s="11"/>
@@ -1895,228 +1770,218 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
-        <v>46284</v>
+        <v>46273</v>
       </c>
       <c r="B30" s="9">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="C30" s="9">
-        <v>60</v>
-      </c>
-      <c r="D30" s="9">
-        <v>120</v>
-      </c>
-      <c r="E30" s="9">
-        <v>40</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="9">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="G30" s="9">
-        <v>1</v>
-      </c>
-      <c r="H30" s="9">
-        <v>150</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H30" s="9"/>
       <c r="I30" s="10">
-        <f t="shared" si="2"/>
-        <v>730</v>
+        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>670</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="3"/>
-        <v>710</v>
-      </c>
-      <c r="K30" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N30" s="12" t="s">
-        <v>60</v>
-      </c>
+        <f>IF(I30="","",1440-I30)</f>
+        <v>770</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>46285</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="9">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="C31" s="9">
-        <v>10</v>
-      </c>
-      <c r="D31" s="9">
-        <v>180</v>
-      </c>
-      <c r="E31" s="9">
-        <v>30</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="9">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G31" s="9">
-        <v>0</v>
-      </c>
-      <c r="H31" s="9">
-        <v>120</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H31" s="9"/>
       <c r="I31" s="10">
-        <f t="shared" si="2"/>
-        <v>880</v>
+        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <v>690</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="3"/>
-        <v>560</v>
-      </c>
-      <c r="K31" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L31" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="12" t="s">
-        <v>61</v>
-      </c>
+        <f>IF(I31="","",1440-I31)</f>
+        <v>750</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
-        <v>46286</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="9">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="C32" s="9">
-        <v>70</v>
-      </c>
-      <c r="D32" s="9">
-        <v>240</v>
-      </c>
-      <c r="E32" s="9">
         <v>80</v>
       </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
       <c r="F32" s="9">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G32" s="9">
-        <v>7</v>
-      </c>
-      <c r="H32" s="9">
-        <v>30</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H32" s="9"/>
       <c r="I32" s="10">
-        <f t="shared" si="2"/>
-        <v>1130</v>
+        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
+        <v>660</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="3"/>
-        <v>310</v>
-      </c>
-      <c r="K32" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>51</v>
-      </c>
+        <f>IF(I32="","",1440-I32)</f>
+        <v>780</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="11"/>
       <c r="N32" s="12"/>
     </row>
-    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>46287</v>
+        <v>46277</v>
       </c>
       <c r="B33" s="9">
-        <v>420</v>
+        <v>120</v>
       </c>
       <c r="C33" s="9">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="D33" s="9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="E33" s="9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F33" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G33" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="2"/>
-        <v>980</v>
+        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <v>480</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="3"/>
-        <v>460</v>
+        <f>IF(I33="","",1440-I33)</f>
+        <v>960</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>46288</v>
-      </c>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>46278</v>
+      </c>
+      <c r="B34" s="9">
+        <v>280</v>
+      </c>
+      <c r="C34" s="9">
+        <v>150</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
+        <v>90</v>
+      </c>
+      <c r="I34" s="10">
+        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
+        <v>520</v>
+      </c>
+      <c r="J34" s="10">
+        <f>IF(I34="","",1440-I34)</f>
+        <v>920</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>46289</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
+        <v>46279</v>
+      </c>
+      <c r="B35" s="9">
+        <v>350</v>
+      </c>
+      <c r="C35" s="9">
+        <v>80</v>
+      </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="F35" s="9">
+        <v>350</v>
+      </c>
+      <c r="G35" s="9">
+        <v>7</v>
+      </c>
       <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I35" s="10">
+        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
+        <v>780</v>
+      </c>
+      <c r="J35" s="10">
+        <f>IF(I35="","",1440-I35)</f>
+        <v>660</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="11"/>
@@ -2125,22 +1990,30 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>46290</v>
-      </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
+        <v>46280</v>
+      </c>
+      <c r="B36" s="9">
+        <v>360</v>
+      </c>
+      <c r="C36" s="9">
+        <v>80</v>
+      </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="9">
+        <v>250</v>
+      </c>
+      <c r="G36" s="9">
+        <v>5</v>
+      </c>
       <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I36" s="10">
+        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <v>690</v>
+      </c>
+      <c r="J36" s="10">
+        <f>IF(I36="","",1440-I36)</f>
+        <v>750</v>
       </c>
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
@@ -2149,22 +2022,30 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
-        <v>46291</v>
-      </c>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
+        <v>46281</v>
+      </c>
+      <c r="B37" s="9">
+        <v>320</v>
+      </c>
+      <c r="C37" s="9">
+        <v>80</v>
+      </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="9">
+        <v>250</v>
+      </c>
+      <c r="G37" s="9">
+        <v>5</v>
+      </c>
       <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I37" s="10">
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>650</v>
+      </c>
+      <c r="J37" s="10">
+        <f>IF(I37="","",1440-I37)</f>
+        <v>790</v>
       </c>
       <c r="K37" s="11"/>
       <c r="L37" s="11"/>
@@ -2173,22 +2054,30 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
-        <v>46292</v>
-      </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
+        <v>46282</v>
+      </c>
+      <c r="B38" s="9">
+        <v>320</v>
+      </c>
+      <c r="C38" s="9">
+        <v>80</v>
+      </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="9">
+        <v>250</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5</v>
+      </c>
       <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="I38" s="10">
+        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <v>650</v>
+      </c>
+      <c r="J38" s="10">
+        <f>IF(I38="","",1440-I38)</f>
+        <v>790</v>
       </c>
       <c r="K38" s="11"/>
       <c r="L38" s="11"/>
@@ -2197,120 +2086,236 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
-        <v>46293</v>
-      </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>46284</v>
+      </c>
+      <c r="B39" s="9">
+        <v>300</v>
+      </c>
+      <c r="C39" s="9">
+        <v>60</v>
+      </c>
+      <c r="D39" s="9">
+        <v>120</v>
+      </c>
+      <c r="E39" s="9">
+        <v>40</v>
+      </c>
+      <c r="F39" s="9">
+        <v>60</v>
+      </c>
+      <c r="G39" s="9">
+        <v>1</v>
+      </c>
+      <c r="H39" s="9">
+        <v>150</v>
+      </c>
+      <c r="I39" s="10">
+        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
+        <v>730</v>
+      </c>
+      <c r="J39" s="10">
+        <f>IF(I39="","",1440-I39)</f>
+        <v>710</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>46294</v>
-      </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>46285</v>
+      </c>
+      <c r="B40" s="9">
+        <v>540</v>
+      </c>
+      <c r="C40" s="9">
+        <v>10</v>
+      </c>
+      <c r="D40" s="9">
+        <v>180</v>
+      </c>
+      <c r="E40" s="9">
+        <v>30</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>120</v>
+      </c>
+      <c r="I40" s="10">
+        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <v>880</v>
+      </c>
+      <c r="J40" s="10">
+        <f>IF(I40="","",1440-I40)</f>
+        <v>560</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
+      <c r="A41" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="9">
+        <v>360</v>
+      </c>
+      <c r="C41" s="9">
+        <v>70</v>
+      </c>
+      <c r="D41" s="9">
+        <v>240</v>
+      </c>
+      <c r="E41" s="9">
+        <v>80</v>
+      </c>
+      <c r="F41" s="9">
+        <v>350</v>
+      </c>
+      <c r="G41" s="9">
+        <v>7</v>
+      </c>
+      <c r="H41" s="9">
+        <v>30</v>
+      </c>
+      <c r="I41" s="10">
+        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <v>1130</v>
+      </c>
+      <c r="J41" s="10">
+        <f>IF(I41="","",1440-I41)</f>
+        <v>310</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="9">
+        <v>420</v>
+      </c>
+      <c r="C42" s="9">
+        <v>80</v>
+      </c>
+      <c r="D42" s="9">
+        <v>180</v>
+      </c>
+      <c r="E42" s="9">
+        <v>30</v>
+      </c>
+      <c r="F42" s="9">
+        <v>250</v>
+      </c>
+      <c r="G42" s="9">
+        <v>5</v>
+      </c>
+      <c r="H42" s="9">
+        <v>20</v>
+      </c>
+      <c r="I42" s="10">
+        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <v>980</v>
+      </c>
+      <c r="J42" s="10">
+        <f>IF(I42="","",1440-I42)</f>
+        <v>460</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="9">
+        <v>420</v>
+      </c>
+      <c r="C43" s="9">
+        <v>80</v>
+      </c>
+      <c r="D43" s="9">
+        <v>150</v>
+      </c>
+      <c r="E43" s="9">
+        <v>60</v>
+      </c>
+      <c r="F43" s="9">
+        <v>240</v>
+      </c>
+      <c r="G43" s="9">
+        <v>4</v>
+      </c>
+      <c r="H43" s="9">
+        <v>30</v>
+      </c>
+      <c r="I43" s="10">
+        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <v>980</v>
+      </c>
+      <c r="J43" s="10">
+        <f>IF(I43="","",1440-I43)</f>
+        <v>460</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
@@ -2319,11 +2324,11 @@
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
         <v/>
       </c>
       <c r="J44" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(I44="","",1440-I44)</f>
         <v/>
       </c>
       <c r="K44" s="11"/>
@@ -2332,7 +2337,9 @@
       <c r="N44" s="12"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
@@ -2341,11 +2348,11 @@
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
         <v/>
       </c>
       <c r="J45" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(I45="","",1440-I45)</f>
         <v/>
       </c>
       <c r="K45" s="11"/>
@@ -2354,7 +2361,9 @@
       <c r="N45" s="12"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
@@ -2363,11 +2372,11 @@
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
         <v/>
       </c>
       <c r="J46" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(I46="","",1440-I46)</f>
         <v/>
       </c>
       <c r="K46" s="11"/>
@@ -2376,7 +2385,9 @@
       <c r="N46" s="12"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
@@ -2385,11 +2396,11 @@
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
         <v/>
       </c>
       <c r="J47" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(I47="","",1440-I47)</f>
         <v/>
       </c>
       <c r="K47" s="11"/>
@@ -2398,7 +2409,9 @@
       <c r="N47" s="12"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
+      <c r="A48" s="8">
+        <v>46293</v>
+      </c>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
@@ -2407,11 +2420,11 @@
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
         <v/>
       </c>
       <c r="J48" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(I48="","",1440-I48)</f>
         <v/>
       </c>
       <c r="K48" s="11"/>
@@ -2420,7 +2433,9 @@
       <c r="N48" s="12"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
@@ -2429,11 +2444,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
         <v/>
       </c>
       <c r="J49" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(I49="","",1440-I49)</f>
         <v/>
       </c>
       <c r="K49" s="11"/>
@@ -2451,11 +2466,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I50:I109" si="6">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
         <v/>
       </c>
       <c r="J50" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J50:J109" si="7">IF(I50="","",1440-I50)</f>
         <v/>
       </c>
       <c r="K50" s="11"/>
@@ -2473,11 +2488,11 @@
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J51" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K51" s="11"/>
@@ -2495,11 +2510,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J52" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K52" s="11"/>
@@ -2517,11 +2532,11 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J53" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K53" s="11"/>
@@ -2539,11 +2554,11 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J54" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K54" s="11"/>
@@ -2561,11 +2576,11 @@
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
       <c r="I55" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J55" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K55" s="11"/>
@@ -2583,11 +2598,11 @@
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J56" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K56" s="11"/>
@@ -2605,11 +2620,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J57" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K57" s="11"/>
@@ -2627,11 +2642,11 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
       <c r="I58" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J58" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K58" s="11"/>
@@ -2649,11 +2664,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J59" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K59" s="11"/>
@@ -2671,11 +2686,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J60" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K60" s="11"/>
@@ -2693,11 +2708,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J61" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K61" s="11"/>
@@ -2715,11 +2730,11 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
       <c r="I62" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J62" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K62" s="11"/>
@@ -2737,11 +2752,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J63" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K63" s="11"/>
@@ -2759,11 +2774,11 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
       <c r="I64" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J64" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K64" s="11"/>
@@ -2781,11 +2796,11 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J65" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K65" s="11"/>
@@ -2803,11 +2818,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -2825,11 +2840,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -2847,11 +2862,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -2869,11 +2884,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J69" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -2891,11 +2906,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2913,11 +2928,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2935,11 +2950,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2957,11 +2972,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" ref="I73:I136" si="4">IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" ref="J73:J136" si="5">IF(I73="","",1440-I73)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2979,11 +2994,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3001,11 +3016,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3023,11 +3038,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3045,11 +3060,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3067,11 +3082,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3089,11 +3104,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3111,11 +3126,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3133,11 +3148,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3155,11 +3170,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3177,11 +3192,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3199,11 +3214,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3221,11 +3236,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3243,11 +3258,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3265,11 +3280,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3287,11 +3302,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3309,11 +3324,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3331,11 +3346,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3353,11 +3368,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3375,11 +3390,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3397,11 +3412,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3419,11 +3434,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3441,11 +3456,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3463,11 +3478,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3485,11 +3500,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3507,11 +3522,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3529,11 +3544,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3551,11 +3566,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3573,11 +3588,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3595,11 +3610,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3617,11 +3632,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3639,11 +3654,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3661,11 +3676,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3683,11 +3698,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3705,11 +3720,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3727,11 +3742,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3749,11 +3764,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3771,11 +3786,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I110:I121" si="8">IF(SUM(B110:F110,H110)=0,"",SUM(B110:F110,H110))</f>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J110:J121" si="9">IF(I110="","",1440-I110)</f>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3793,11 +3808,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3815,11 +3830,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3837,11 +3852,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3859,11 +3874,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3881,11 +3896,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3903,11 +3918,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3925,11 +3940,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3947,11 +3962,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3969,11 +3984,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -3991,11 +4006,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4013,610 +4028,16 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="11"/>
       <c r="L121" s="11"/>
       <c r="M121" s="11"/>
-      <c r="N121" s="12"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A122" s="8"/>
-      <c r="B122" s="9"/>
-      <c r="C122" s="9"/>
-      <c r="D122" s="9"/>
-      <c r="E122" s="9"/>
-      <c r="F122" s="9"/>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
-      <c r="I122" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J122" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K122" s="11"/>
-      <c r="L122" s="11"/>
-      <c r="M122" s="11"/>
-      <c r="N122" s="12"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A123" s="8"/>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9"/>
-      <c r="G123" s="9"/>
-      <c r="H123" s="9"/>
-      <c r="I123" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J123" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K123" s="11"/>
-      <c r="L123" s="11"/>
-      <c r="M123" s="11"/>
-      <c r="N123" s="12"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A124" s="8"/>
-      <c r="B124" s="9"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="9"/>
-      <c r="E124" s="9"/>
-      <c r="F124" s="9"/>
-      <c r="G124" s="9"/>
-      <c r="H124" s="9"/>
-      <c r="I124" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J124" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K124" s="11"/>
-      <c r="L124" s="11"/>
-      <c r="M124" s="11"/>
-      <c r="N124" s="12"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A125" s="8"/>
-      <c r="B125" s="9"/>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-      <c r="E125" s="9"/>
-      <c r="F125" s="9"/>
-      <c r="G125" s="9"/>
-      <c r="H125" s="9"/>
-      <c r="I125" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J125" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K125" s="11"/>
-      <c r="L125" s="11"/>
-      <c r="M125" s="11"/>
-      <c r="N125" s="12"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A126" s="8"/>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9"/>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
-      <c r="I126" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J126" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K126" s="11"/>
-      <c r="L126" s="11"/>
-      <c r="M126" s="11"/>
-      <c r="N126" s="12"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A127" s="8"/>
-      <c r="B127" s="9"/>
-      <c r="C127" s="9"/>
-      <c r="D127" s="9"/>
-      <c r="E127" s="9"/>
-      <c r="F127" s="9"/>
-      <c r="G127" s="9"/>
-      <c r="H127" s="9"/>
-      <c r="I127" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J127" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K127" s="11"/>
-      <c r="L127" s="11"/>
-      <c r="M127" s="11"/>
-      <c r="N127" s="12"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A128" s="8"/>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="9"/>
-      <c r="H128" s="9"/>
-      <c r="I128" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J128" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K128" s="11"/>
-      <c r="L128" s="11"/>
-      <c r="M128" s="11"/>
-      <c r="N128" s="12"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A129" s="8"/>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9"/>
-      <c r="G129" s="9"/>
-      <c r="H129" s="9"/>
-      <c r="I129" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J129" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K129" s="11"/>
-      <c r="L129" s="11"/>
-      <c r="M129" s="11"/>
-      <c r="N129" s="12"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A130" s="8"/>
-      <c r="B130" s="9"/>
-      <c r="C130" s="9"/>
-      <c r="D130" s="9"/>
-      <c r="E130" s="9"/>
-      <c r="F130" s="9"/>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J130" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K130" s="11"/>
-      <c r="L130" s="11"/>
-      <c r="M130" s="11"/>
-      <c r="N130" s="12"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A131" s="8"/>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="9"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J131" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K131" s="11"/>
-      <c r="L131" s="11"/>
-      <c r="M131" s="11"/>
-      <c r="N131" s="12"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A132" s="8"/>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="9"/>
-      <c r="H132" s="9"/>
-      <c r="I132" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J132" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K132" s="11"/>
-      <c r="L132" s="11"/>
-      <c r="M132" s="11"/>
-      <c r="N132" s="12"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A133" s="8"/>
-      <c r="B133" s="9"/>
-      <c r="C133" s="9"/>
-      <c r="D133" s="9"/>
-      <c r="E133" s="9"/>
-      <c r="F133" s="9"/>
-      <c r="G133" s="9"/>
-      <c r="H133" s="9"/>
-      <c r="I133" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J133" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K133" s="11"/>
-      <c r="L133" s="11"/>
-      <c r="M133" s="11"/>
-      <c r="N133" s="12"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A134" s="8"/>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9"/>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
-      <c r="I134" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J134" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K134" s="11"/>
-      <c r="L134" s="11"/>
-      <c r="M134" s="11"/>
-      <c r="N134" s="12"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A135" s="8"/>
-      <c r="B135" s="9"/>
-      <c r="C135" s="9"/>
-      <c r="D135" s="9"/>
-      <c r="E135" s="9"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="9"/>
-      <c r="H135" s="9"/>
-      <c r="I135" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J135" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K135" s="11"/>
-      <c r="L135" s="11"/>
-      <c r="M135" s="11"/>
-      <c r="N135" s="12"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A136" s="8"/>
-      <c r="B136" s="9"/>
-      <c r="C136" s="9"/>
-      <c r="D136" s="9"/>
-      <c r="E136" s="9"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="9"/>
-      <c r="H136" s="9"/>
-      <c r="I136" s="10" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J136" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K136" s="11"/>
-      <c r="L136" s="11"/>
-      <c r="M136" s="11"/>
-      <c r="N136" s="12"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A137" s="8"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="9"/>
-      <c r="D137" s="9"/>
-      <c r="E137" s="9"/>
-      <c r="F137" s="9"/>
-      <c r="G137" s="9"/>
-      <c r="H137" s="9"/>
-      <c r="I137" s="10" t="str">
-        <f t="shared" ref="I137:I148" si="6">IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
-        <v/>
-      </c>
-      <c r="J137" s="10" t="str">
-        <f t="shared" ref="J137:J148" si="7">IF(I137="","",1440-I137)</f>
-        <v/>
-      </c>
-      <c r="K137" s="11"/>
-      <c r="L137" s="11"/>
-      <c r="M137" s="11"/>
-      <c r="N137" s="12"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A138" s="8"/>
-      <c r="B138" s="9"/>
-      <c r="C138" s="9"/>
-      <c r="D138" s="9"/>
-      <c r="E138" s="9"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
-      <c r="I138" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J138" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K138" s="11"/>
-      <c r="L138" s="11"/>
-      <c r="M138" s="11"/>
-      <c r="N138" s="12"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A139" s="8"/>
-      <c r="B139" s="9"/>
-      <c r="C139" s="9"/>
-      <c r="D139" s="9"/>
-      <c r="E139" s="9"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="9"/>
-      <c r="H139" s="9"/>
-      <c r="I139" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J139" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K139" s="11"/>
-      <c r="L139" s="11"/>
-      <c r="M139" s="11"/>
-      <c r="N139" s="12"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A140" s="8"/>
-      <c r="B140" s="9"/>
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
-      <c r="I140" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J140" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K140" s="11"/>
-      <c r="L140" s="11"/>
-      <c r="M140" s="11"/>
-      <c r="N140" s="12"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A141" s="8"/>
-      <c r="B141" s="9"/>
-      <c r="C141" s="9"/>
-      <c r="D141" s="9"/>
-      <c r="E141" s="9"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="9"/>
-      <c r="H141" s="9"/>
-      <c r="I141" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J141" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K141" s="11"/>
-      <c r="L141" s="11"/>
-      <c r="M141" s="11"/>
-      <c r="N141" s="12"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A142" s="8"/>
-      <c r="B142" s="9"/>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J142" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K142" s="11"/>
-      <c r="L142" s="11"/>
-      <c r="M142" s="11"/>
-      <c r="N142" s="12"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A143" s="8"/>
-      <c r="B143" s="9"/>
-      <c r="C143" s="9"/>
-      <c r="D143" s="9"/>
-      <c r="E143" s="9"/>
-      <c r="F143" s="9"/>
-      <c r="G143" s="9"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J143" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K143" s="11"/>
-      <c r="L143" s="11"/>
-      <c r="M143" s="11"/>
-      <c r="N143" s="12"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A144" s="8"/>
-      <c r="B144" s="9"/>
-      <c r="C144" s="9"/>
-      <c r="D144" s="9"/>
-      <c r="E144" s="9"/>
-      <c r="F144" s="9"/>
-      <c r="G144" s="9"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J144" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K144" s="11"/>
-      <c r="L144" s="11"/>
-      <c r="M144" s="11"/>
-      <c r="N144" s="12"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A145" s="8"/>
-      <c r="B145" s="9"/>
-      <c r="C145" s="9"/>
-      <c r="D145" s="9"/>
-      <c r="E145" s="9"/>
-      <c r="F145" s="9"/>
-      <c r="G145" s="9"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J145" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K145" s="11"/>
-      <c r="L145" s="11"/>
-      <c r="M145" s="11"/>
-      <c r="N145" s="12"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A146" s="8"/>
-      <c r="B146" s="9"/>
-      <c r="C146" s="9"/>
-      <c r="D146" s="9"/>
-      <c r="E146" s="9"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
-      <c r="I146" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J146" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K146" s="11"/>
-      <c r="L146" s="11"/>
-      <c r="M146" s="11"/>
-      <c r="N146" s="12"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A147" s="8"/>
-      <c r="B147" s="9"/>
-      <c r="C147" s="9"/>
-      <c r="D147" s="9"/>
-      <c r="E147" s="9"/>
-      <c r="F147" s="9"/>
-      <c r="G147" s="9"/>
-      <c r="H147" s="9"/>
-      <c r="I147" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J147" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K147" s="11"/>
-      <c r="L147" s="11"/>
-      <c r="M147" s="11"/>
-      <c r="N147" s="12"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A148" s="8"/>
-      <c r="B148" s="9"/>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J148" s="10" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K148" s="11"/>
-      <c r="L148" s="11"/>
-      <c r="M148" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -4627,21 +4048,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J148">
+  <conditionalFormatting sqref="J6:J121">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K148" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K121" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L148" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L121" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M148" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M121" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A11A9E4-EDE1-4556-8B6D-D15F550CB1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E81D11-C8DC-41A4-8958-E09BB89A21DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,18 @@
   </si>
   <si>
     <t>I have a CA tomorrow, but I’m not feeling well, so I’m unable to study for it.</t>
+  </si>
+  <si>
+    <t>Back to routine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Started planning for Mid term examination </t>
+  </si>
+  <si>
+    <t>Focused on the python coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Got good mark in Network CA </t>
   </si>
 </sst>
 </file>
@@ -388,7 +400,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -419,6 +431,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,10 +968,10 @@
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
@@ -1024,20 +1039,24 @@
       <c r="A6" s="8">
         <v>46247</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="B6" s="9">
+        <v>360</v>
+      </c>
+      <c r="C6" s="9">
+        <v>80</v>
+      </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="10" t="str">
+      <c r="I6" s="10">
         <f t="shared" ref="I6:I13" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v/>
-      </c>
-      <c r="J6" s="10" t="str">
+        <v>440</v>
+      </c>
+      <c r="J6" s="10">
         <f t="shared" ref="J6:J13" si="1">IF(I6="","",1440-I6)</f>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
@@ -1048,20 +1067,24 @@
       <c r="A7" s="8">
         <v>46248</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
+      <c r="B7" s="9">
+        <v>420</v>
+      </c>
+      <c r="C7" s="9">
+        <v>80</v>
+      </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="10" t="str">
+      <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>940</v>
       </c>
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
@@ -1072,20 +1095,24 @@
       <c r="A8" s="8">
         <v>46249</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
+      <c r="B8" s="9">
+        <v>480</v>
+      </c>
+      <c r="C8" s="9">
+        <v>120</v>
+      </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="10" t="str">
+      <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>840</v>
       </c>
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
@@ -1096,20 +1123,24 @@
       <c r="A9" s="8">
         <v>46250</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
+      <c r="B9" s="9">
+        <v>480</v>
+      </c>
+      <c r="C9" s="9">
+        <v>10</v>
+      </c>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>490</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>950</v>
       </c>
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
@@ -1120,20 +1151,24 @@
       <c r="A10" s="8">
         <v>46251</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
+      <c r="B10" s="9">
+        <v>420</v>
+      </c>
+      <c r="C10" s="9">
+        <v>80</v>
+      </c>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>940</v>
       </c>
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
@@ -1144,20 +1179,24 @@
       <c r="A11" s="8">
         <v>46252</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
+      <c r="B11" s="9">
+        <v>360</v>
+      </c>
+      <c r="C11" s="9">
+        <v>80</v>
+      </c>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>440</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
@@ -1168,20 +1207,24 @@
       <c r="A12" s="8">
         <v>46253</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
+      <c r="B12" s="9">
+        <v>420</v>
+      </c>
+      <c r="C12" s="9">
+        <v>80</v>
+      </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>940</v>
       </c>
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
@@ -1192,20 +1235,24 @@
       <c r="A13" s="8">
         <v>46254</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
+      <c r="B13" s="9">
+        <v>420</v>
+      </c>
+      <c r="C13" s="9">
+        <v>80</v>
+      </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
+        <v>940</v>
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
@@ -1216,20 +1263,24 @@
       <c r="A14" s="8">
         <v>46255</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
+      <c r="B14" s="9">
+        <v>420</v>
+      </c>
+      <c r="C14" s="9">
+        <v>80</v>
+      </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="I14" s="10">
         <f t="shared" ref="I14:I18" si="2">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" ref="J14:J18" si="3">IF(I14="","",1440-I14)</f>
-        <v/>
+        <v>940</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -1240,20 +1291,24 @@
       <c r="A15" s="8">
         <v>46256</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
+      <c r="B15" s="9">
+        <v>480</v>
+      </c>
+      <c r="C15" s="9">
+        <v>120</v>
+      </c>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="I15" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>600</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>840</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
@@ -1264,20 +1319,24 @@
       <c r="A16" s="8">
         <v>46257</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
+      <c r="B16" s="9">
+        <v>480</v>
+      </c>
+      <c r="C16" s="9">
+        <v>10</v>
+      </c>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="I16" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>490</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>950</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
@@ -1288,20 +1347,24 @@
       <c r="A17" s="8">
         <v>46258</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="B17" s="9">
+        <v>360</v>
+      </c>
+      <c r="C17" s="9">
+        <v>80</v>
+      </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="I17" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>440</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
@@ -1312,20 +1375,24 @@
       <c r="A18" s="8">
         <v>46259</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
+      <c r="B18" s="9">
+        <v>420</v>
+      </c>
+      <c r="C18" s="9">
+        <v>80</v>
+      </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="I18" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>500</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="3"/>
-        <v/>
+        <v>940</v>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
@@ -1346,7 +1413,7 @@
         <v>210</v>
       </c>
       <c r="E19" s="9">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F19" s="9">
         <v>200</v>
@@ -1359,11 +1426,11 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" ref="I19:I21" si="4">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" ref="J19:J21" si="5">IF(I19="","",1440-I19)</f>
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>56</v>
@@ -1484,7 +1551,7 @@
         <v>260</v>
       </c>
       <c r="E22" s="9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -1496,12 +1563,12 @@
         <v>30</v>
       </c>
       <c r="I22" s="10">
-        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" ref="I22:I49" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>730</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" ref="J22:J49" si="7">IF(I22="","",1440-I22)</f>
         <v>710</v>
-      </c>
-      <c r="J22" s="10">
-        <f>IF(I22="","",1440-I22)</f>
-        <v>730</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>57</v>
@@ -1542,11 +1609,11 @@
         <v>10</v>
       </c>
       <c r="I23" s="10">
-        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <f t="shared" si="6"/>
         <v>800</v>
       </c>
       <c r="J23" s="10">
-        <f>IF(I23="","",1440-I23)</f>
+        <f t="shared" si="7"/>
         <v>640</v>
       </c>
       <c r="K23" s="11" t="s">
@@ -1576,7 +1643,7 @@
         <v>150</v>
       </c>
       <c r="E24" s="9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F24" s="9">
         <v>350</v>
@@ -1588,12 +1655,12 @@
         <v>60</v>
       </c>
       <c r="I24" s="10">
-        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
-        <v>1065</v>
+        <f t="shared" si="6"/>
+        <v>1080</v>
       </c>
       <c r="J24" s="10">
-        <f>IF(I24="","",1440-I24)</f>
-        <v>375</v>
+        <f t="shared" si="7"/>
+        <v>360</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>56</v>
@@ -1628,11 +1695,11 @@
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="10">
-        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <f t="shared" si="6"/>
         <v>740</v>
       </c>
       <c r="J25" s="10">
-        <f>IF(I25="","",1440-I25)</f>
+        <f t="shared" si="7"/>
         <v>700</v>
       </c>
       <c r="K25" s="11"/>
@@ -1660,11 +1727,11 @@
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="10">
-        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <f t="shared" si="6"/>
         <v>720</v>
       </c>
       <c r="J26" s="10">
-        <f>IF(I26="","",1440-I26)</f>
+        <f t="shared" si="7"/>
         <v>720</v>
       </c>
       <c r="K26" s="11"/>
@@ -1692,11 +1759,11 @@
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="10">
-        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="J27" s="10">
-        <f>IF(I27="","",1440-I27)</f>
+        <f t="shared" si="7"/>
         <v>940</v>
       </c>
       <c r="K27" s="11"/>
@@ -1724,11 +1791,11 @@
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="10">
-        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="J28" s="10">
-        <f>IF(I28="","",1440-I28)</f>
+        <f t="shared" si="7"/>
         <v>920</v>
       </c>
       <c r="K28" s="11"/>
@@ -1756,11 +1823,11 @@
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="10">
-        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <f t="shared" si="6"/>
         <v>840</v>
       </c>
       <c r="J29" s="10">
-        <f>IF(I29="","",1440-I29)</f>
+        <f t="shared" si="7"/>
         <v>600</v>
       </c>
       <c r="K29" s="11"/>
@@ -1788,11 +1855,11 @@
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="10">
-        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <f t="shared" si="6"/>
         <v>670</v>
       </c>
       <c r="J30" s="10">
-        <f>IF(I30="","",1440-I30)</f>
+        <f t="shared" si="7"/>
         <v>770</v>
       </c>
       <c r="K30" s="11"/>
@@ -1820,11 +1887,11 @@
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="10">
-        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <f t="shared" si="6"/>
         <v>690</v>
       </c>
       <c r="J31" s="10">
-        <f>IF(I31="","",1440-I31)</f>
+        <f t="shared" si="7"/>
         <v>750</v>
       </c>
       <c r="K31" s="11"/>
@@ -1852,11 +1919,11 @@
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="10">
-        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
+        <f t="shared" si="6"/>
         <v>660</v>
       </c>
       <c r="J32" s="10">
-        <f>IF(I32="","",1440-I32)</f>
+        <f t="shared" si="7"/>
         <v>780</v>
       </c>
       <c r="K32" s="11"/>
@@ -1890,11 +1957,11 @@
         <v>150</v>
       </c>
       <c r="I33" s="10">
-        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <f t="shared" si="6"/>
         <v>480</v>
       </c>
       <c r="J33" s="10">
-        <f>IF(I33="","",1440-I33)</f>
+        <f t="shared" si="7"/>
         <v>960</v>
       </c>
       <c r="K33" s="11" t="s">
@@ -1936,11 +2003,11 @@
         <v>90</v>
       </c>
       <c r="I34" s="10">
-        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="J34" s="10">
-        <f>IF(I34="","",1440-I34)</f>
+        <f t="shared" si="7"/>
         <v>920</v>
       </c>
       <c r="K34" s="11" t="s">
@@ -1966,27 +2033,41 @@
       <c r="C35" s="9">
         <v>80</v>
       </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="D35" s="9">
+        <v>180</v>
+      </c>
+      <c r="E35" s="9">
+        <v>50</v>
+      </c>
       <c r="F35" s="9">
         <v>350</v>
       </c>
       <c r="G35" s="9">
         <v>7</v>
       </c>
-      <c r="H35" s="9"/>
+      <c r="H35" s="9">
+        <v>20</v>
+      </c>
       <c r="I35" s="10">
-        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
-        <v>780</v>
+        <f t="shared" si="6"/>
+        <v>1030</v>
       </c>
       <c r="J35" s="10">
-        <f>IF(I35="","",1440-I35)</f>
-        <v>660</v>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <f t="shared" si="7"/>
+        <v>410</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
@@ -1998,27 +2079,41 @@
       <c r="C36" s="9">
         <v>80</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="D36" s="9">
+        <v>180</v>
+      </c>
+      <c r="E36" s="9">
+        <v>60</v>
+      </c>
       <c r="F36" s="9">
         <v>250</v>
       </c>
       <c r="G36" s="9">
         <v>5</v>
       </c>
-      <c r="H36" s="9"/>
+      <c r="H36" s="9">
+        <v>60</v>
+      </c>
       <c r="I36" s="10">
-        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
-        <v>690</v>
+        <f t="shared" si="6"/>
+        <v>990</v>
       </c>
       <c r="J36" s="10">
-        <f>IF(I36="","",1440-I36)</f>
-        <v>750</v>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+        <f t="shared" si="7"/>
+        <v>450</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
@@ -2030,27 +2125,41 @@
       <c r="C37" s="9">
         <v>80</v>
       </c>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
+      <c r="D37" s="9">
+        <v>210</v>
+      </c>
+      <c r="E37" s="9">
+        <v>60</v>
+      </c>
       <c r="F37" s="9">
         <v>250</v>
       </c>
       <c r="G37" s="9">
         <v>5</v>
       </c>
-      <c r="H37" s="9"/>
+      <c r="H37" s="9">
+        <v>120</v>
+      </c>
       <c r="I37" s="10">
-        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
-        <v>650</v>
+        <f t="shared" si="6"/>
+        <v>1040</v>
       </c>
       <c r="J37" s="10">
-        <f>IF(I37="","",1440-I37)</f>
-        <v>790</v>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
+        <f t="shared" si="7"/>
+        <v>400</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
@@ -2062,27 +2171,41 @@
       <c r="C38" s="9">
         <v>80</v>
       </c>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
+      <c r="D38" s="9">
+        <v>120</v>
+      </c>
+      <c r="E38" s="9">
+        <v>20</v>
+      </c>
       <c r="F38" s="9">
         <v>250</v>
       </c>
       <c r="G38" s="9">
         <v>5</v>
       </c>
-      <c r="H38" s="9"/>
+      <c r="H38" s="9">
+        <v>0</v>
+      </c>
       <c r="I38" s="10">
-        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <f t="shared" si="6"/>
+        <v>790</v>
+      </c>
+      <c r="J38" s="10">
+        <f t="shared" si="7"/>
         <v>650</v>
       </c>
-      <c r="J38" s="10">
-        <f>IF(I38="","",1440-I38)</f>
-        <v>790</v>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
+      <c r="K38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
@@ -2098,7 +2221,7 @@
         <v>120</v>
       </c>
       <c r="E39" s="9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F39" s="9">
         <v>60</v>
@@ -2110,12 +2233,12 @@
         <v>150</v>
       </c>
       <c r="I39" s="10">
-        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
-        <v>730</v>
+        <f t="shared" si="6"/>
+        <v>750</v>
       </c>
       <c r="J39" s="10">
-        <f>IF(I39="","",1440-I39)</f>
-        <v>710</v>
+        <f t="shared" si="7"/>
+        <v>690</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>56</v>
@@ -2156,11 +2279,11 @@
         <v>120</v>
       </c>
       <c r="I40" s="10">
-        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <f t="shared" si="6"/>
         <v>880</v>
       </c>
       <c r="J40" s="10">
-        <f>IF(I40="","",1440-I40)</f>
+        <f t="shared" si="7"/>
         <v>560</v>
       </c>
       <c r="K40" s="11" t="s">
@@ -2202,11 +2325,11 @@
         <v>30</v>
       </c>
       <c r="I41" s="10">
-        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <f t="shared" si="6"/>
         <v>1130</v>
       </c>
       <c r="J41" s="10">
-        <f>IF(I41="","",1440-I41)</f>
+        <f t="shared" si="7"/>
         <v>310</v>
       </c>
       <c r="K41" s="11" t="s">
@@ -2218,7 +2341,9 @@
       <c r="M41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N41" s="12"/>
+      <c r="N41" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
@@ -2246,11 +2371,11 @@
         <v>20</v>
       </c>
       <c r="I42" s="10">
-        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <f t="shared" si="6"/>
         <v>980</v>
       </c>
       <c r="J42" s="10">
-        <f>IF(I42="","",1440-I42)</f>
+        <f t="shared" si="7"/>
         <v>460</v>
       </c>
       <c r="K42" s="11" t="s">
@@ -2292,11 +2417,11 @@
         <v>30</v>
       </c>
       <c r="I43" s="10">
-        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <f t="shared" si="6"/>
         <v>980</v>
       </c>
       <c r="J43" s="10">
-        <f>IF(I43="","",1440-I43)</f>
+        <f t="shared" si="7"/>
         <v>460</v>
       </c>
       <c r="K43" s="11" t="s">
@@ -2324,11 +2449,11 @@
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
       <c r="I44" s="10" t="str">
-        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J44" s="10" t="str">
-        <f>IF(I44="","",1440-I44)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K44" s="11"/>
@@ -2348,11 +2473,11 @@
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="10" t="str">
-        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J45" s="10" t="str">
-        <f>IF(I45="","",1440-I45)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K45" s="11"/>
@@ -2372,11 +2497,11 @@
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="10" t="str">
-        <f>IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J46" s="10" t="str">
-        <f>IF(I46="","",1440-I46)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K46" s="11"/>
@@ -2396,11 +2521,11 @@
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="10" t="str">
-        <f>IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J47" s="10" t="str">
-        <f>IF(I47="","",1440-I47)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K47" s="11"/>
@@ -2420,11 +2545,11 @@
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="10" t="str">
-        <f>IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J48" s="10" t="str">
-        <f>IF(I48="","",1440-I48)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K48" s="11"/>
@@ -2444,11 +2569,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="10" t="str">
-        <f>IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J49" s="10" t="str">
-        <f>IF(I49="","",1440-I49)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K49" s="11"/>
@@ -2466,11 +2591,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="10" t="str">
-        <f t="shared" ref="I50:I109" si="6">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
+        <f t="shared" ref="I50:I109" si="8">IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
         <v/>
       </c>
       <c r="J50" s="10" t="str">
-        <f t="shared" ref="J50:J109" si="7">IF(I50="","",1440-I50)</f>
+        <f t="shared" ref="J50:J109" si="9">IF(I50="","",1440-I50)</f>
         <v/>
       </c>
       <c r="K50" s="11"/>
@@ -2488,11 +2613,11 @@
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J51" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K51" s="11"/>
@@ -2510,11 +2635,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J52" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K52" s="11"/>
@@ -2532,11 +2657,11 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J53" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K53" s="11"/>
@@ -2554,11 +2679,11 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J54" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K54" s="11"/>
@@ -2576,11 +2701,11 @@
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
       <c r="I55" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J55" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K55" s="11"/>
@@ -2598,11 +2723,11 @@
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J56" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K56" s="11"/>
@@ -2620,11 +2745,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J57" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K57" s="11"/>
@@ -2642,11 +2767,11 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
       <c r="I58" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J58" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K58" s="11"/>
@@ -2664,11 +2789,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J59" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K59" s="11"/>
@@ -2686,11 +2811,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J60" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K60" s="11"/>
@@ -2708,11 +2833,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J61" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K61" s="11"/>
@@ -2730,11 +2855,11 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
       <c r="I62" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J62" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K62" s="11"/>
@@ -2752,11 +2877,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J63" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K63" s="11"/>
@@ -2774,11 +2899,11 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
       <c r="I64" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J64" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K64" s="11"/>
@@ -2796,11 +2921,11 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J65" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K65" s="11"/>
@@ -2818,11 +2943,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J66" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -2840,11 +2965,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J67" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -2862,11 +2987,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J68" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -2884,11 +3009,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J69" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -2906,11 +3031,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J70" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -2928,11 +3053,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J71" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -2950,11 +3075,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J72" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -2972,11 +3097,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J73" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -2994,11 +3119,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J74" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3016,11 +3141,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J75" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3038,11 +3163,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J76" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3060,11 +3185,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J77" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3082,11 +3207,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J78" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3104,11 +3229,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J79" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3126,11 +3251,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J80" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3148,11 +3273,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J81" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3170,11 +3295,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J82" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3192,11 +3317,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J83" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3214,11 +3339,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J84" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3236,11 +3361,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J85" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3258,11 +3383,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J86" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3280,11 +3405,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J87" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3302,11 +3427,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J88" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3324,11 +3449,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J89" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3346,11 +3471,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J90" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3368,11 +3493,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J91" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3390,11 +3515,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J92" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3412,11 +3537,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J93" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3434,11 +3559,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J94" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3456,11 +3581,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J95" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3478,11 +3603,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J96" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3500,11 +3625,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J97" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3522,11 +3647,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J98" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3544,11 +3669,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J99" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3566,11 +3691,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J100" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3588,11 +3713,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J101" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -3610,11 +3735,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J102" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -3632,11 +3757,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J103" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -3654,11 +3779,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J104" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -3676,11 +3801,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J105" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -3698,11 +3823,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J106" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -3720,11 +3845,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J107" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -3742,11 +3867,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J108" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -3764,11 +3889,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J109" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -3786,11 +3911,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="10" t="str">
-        <f t="shared" ref="I110:I121" si="8">IF(SUM(B110:F110,H110)=0,"",SUM(B110:F110,H110))</f>
+        <f t="shared" ref="I110:I121" si="10">IF(SUM(B110:F110,H110)=0,"",SUM(B110:F110,H110))</f>
         <v/>
       </c>
       <c r="J110" s="10" t="str">
-        <f t="shared" ref="J110:J121" si="9">IF(I110="","",1440-I110)</f>
+        <f t="shared" ref="J110:J121" si="11">IF(I110="","",1440-I110)</f>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -3808,11 +3933,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J111" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -3830,11 +3955,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J112" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -3852,11 +3977,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J113" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -3874,11 +3999,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J114" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -3896,11 +4021,11 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J115" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K115" s="11"/>
@@ -3918,11 +4043,11 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J116" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K116" s="11"/>
@@ -3940,11 +4065,11 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J117" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K117" s="11"/>
@@ -3962,11 +4087,11 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J118" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K118" s="11"/>
@@ -3984,11 +4109,11 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J119" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K119" s="11"/>
@@ -4006,11 +4131,11 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J120" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K120" s="11"/>
@@ -4028,11 +4153,11 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J121" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K121" s="11"/>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\MInor Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9945AE-4345-49A4-AFE3-FFC936C016D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9558770-D0F8-49C3-945D-B8ABC7A2F329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Played football after a long time.</t>
+  </si>
+  <si>
+    <t>Started my daily recording.</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1090,9 @@
       <c r="M6" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N6" s="12"/>
+      <c r="N6" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
@@ -1833,7 +1838,7 @@
         <v>800</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="7"/>
+        <f>IF(I23="","",1440-I23)</f>
         <v>640</v>
       </c>
       <c r="K23" s="11" t="s">
@@ -1903,7 +1908,7 @@
         <v>420</v>
       </c>
       <c r="C25" s="9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D25" s="9">
         <v>60</v>
@@ -1917,62 +1922,114 @@
       <c r="G25" s="9">
         <v>5</v>
       </c>
-      <c r="H25" s="9"/>
+      <c r="H25" s="9">
+        <v>0</v>
+      </c>
       <c r="I25" s="10">
         <f t="shared" si="6"/>
-        <v>800</v>
+        <v>810</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="7"/>
-        <v>640</v>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
+        <v>630</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N25" s="12"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>46267</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="B26" s="9">
+        <v>360</v>
+      </c>
+      <c r="C26" s="9">
+        <v>80</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
       <c r="F26" s="9">
         <v>200</v>
       </c>
       <c r="G26" s="9">
         <v>4</v>
       </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
+      <c r="H26" s="9">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10">
+        <f t="shared" si="6"/>
+        <v>640</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="7"/>
+        <v>800</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N26" s="12"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>46268</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
+      <c r="B27" s="9">
+        <v>360</v>
+      </c>
+      <c r="C27" s="9">
+        <v>80</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
       <c r="F27" s="9">
         <v>250</v>
       </c>
       <c r="G27" s="9">
         <v>5</v>
       </c>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
+      <c r="H27" s="9">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
+        <f t="shared" si="6"/>
+        <v>690</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="7"/>
+        <v>750</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="12"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -1985,15 +2042,21 @@
       <c r="C28" s="9">
         <v>80</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0</v>
+      </c>
       <c r="F28" s="9">
         <v>300</v>
       </c>
       <c r="G28" s="9">
         <v>6</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="9">
+        <v>0</v>
+      </c>
       <c r="I28" s="10">
         <f t="shared" si="6"/>
         <v>720</v>
@@ -2002,9 +2065,15 @@
         <f t="shared" si="7"/>
         <v>720</v>
       </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
+      <c r="K28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="12"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2015,28 +2084,40 @@
         <v>420</v>
       </c>
       <c r="C29" s="9">
-        <v>80</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+        <v>120</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
       <c r="F29" s="9">
         <v>0</v>
       </c>
       <c r="G29" s="9">
         <v>0</v>
       </c>
-      <c r="H29" s="9"/>
+      <c r="H29" s="9">
+        <v>0</v>
+      </c>
       <c r="I29" s="10">
         <f t="shared" si="6"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="J29" s="10">
         <f t="shared" si="7"/>
-        <v>940</v>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
+        <v>900</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N29" s="12"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2047,28 +2128,40 @@
         <v>440</v>
       </c>
       <c r="C30" s="9">
-        <v>80</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+        <v>10</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
       <c r="F30" s="9">
         <v>0</v>
       </c>
       <c r="G30" s="9">
         <v>0</v>
       </c>
-      <c r="H30" s="9"/>
+      <c r="H30" s="9">
+        <v>0</v>
+      </c>
       <c r="I30" s="10">
         <f t="shared" si="6"/>
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="J30" s="10">
         <f t="shared" si="7"/>
-        <v>920</v>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
+        <v>990</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="12"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2081,15 +2174,21 @@
       <c r="C31" s="9">
         <v>80</v>
       </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0</v>
+      </c>
       <c r="F31" s="9">
         <v>350</v>
       </c>
       <c r="G31" s="9">
         <v>7</v>
       </c>
-      <c r="H31" s="9"/>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
       <c r="I31" s="10">
         <f t="shared" si="6"/>
         <v>840</v>
@@ -2098,9 +2197,15 @@
         <f t="shared" si="7"/>
         <v>600</v>
       </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
+      <c r="K31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N31" s="12"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2113,15 +2218,21 @@
       <c r="C32" s="9">
         <v>80</v>
       </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0</v>
+      </c>
       <c r="F32" s="9">
         <v>250</v>
       </c>
       <c r="G32" s="9">
         <v>5</v>
       </c>
-      <c r="H32" s="9"/>
+      <c r="H32" s="9">
+        <v>0</v>
+      </c>
       <c r="I32" s="10">
         <f t="shared" si="6"/>
         <v>670</v>
@@ -2130,31 +2241,59 @@
         <f t="shared" si="7"/>
         <v>770</v>
       </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
+      <c r="K32" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="12"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>46274</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="B33" s="9">
+        <v>420</v>
+      </c>
+      <c r="C33" s="9">
+        <v>80</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0</v>
+      </c>
       <c r="F33" s="9">
         <v>200</v>
       </c>
       <c r="G33" s="9">
         <v>4</v>
       </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
+      <c r="H33" s="9">
+        <v>0</v>
+      </c>
+      <c r="I33" s="10">
+        <f t="shared" si="6"/>
+        <v>700</v>
+      </c>
+      <c r="J33" s="10">
+        <f t="shared" si="7"/>
+        <v>740</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="12"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2529,22 +2668,44 @@
       <c r="A42" s="8">
         <v>46283</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
+      <c r="B42" s="9">
+        <v>420</v>
+      </c>
+      <c r="C42" s="9">
+        <v>80</v>
+      </c>
+      <c r="D42" s="9">
+        <v>170</v>
+      </c>
+      <c r="E42" s="9">
+        <v>50</v>
+      </c>
       <c r="F42" s="9">
         <v>300</v>
       </c>
       <c r="G42" s="9">
         <v>6</v>
       </c>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
+      <c r="H42" s="9">
+        <v>30</v>
+      </c>
+      <c r="I42" s="10">
+        <f t="shared" si="6"/>
+        <v>1050</v>
+      </c>
+      <c r="J42" s="10">
+        <f t="shared" si="7"/>
+        <v>390</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N42" s="12"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\MInor Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9558770-D0F8-49C3-945D-B8ABC7A2F329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0F1F00-EF74-4F56-B43F-C46E180FC0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1286,7 +1286,7 @@
         <v>120</v>
       </c>
       <c r="E11" s="9">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="F11" s="9">
         <v>250</v>
@@ -1299,11 +1299,11 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>940</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>49</v>
@@ -1506,7 +1506,7 @@
         <v>300</v>
       </c>
       <c r="E16" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -1519,11 +1519,11 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="2"/>
-        <v>810</v>
+        <v>860</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="3"/>
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>57</v>
@@ -1776,7 +1776,7 @@
         <v>260</v>
       </c>
       <c r="E22" s="9">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -1789,11 +1789,11 @@
       </c>
       <c r="I22" s="10">
         <f t="shared" ref="I22:I52" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v>730</v>
+        <v>790</v>
       </c>
       <c r="J22" s="10">
         <f t="shared" ref="J22:J52" si="7">IF(I22="","",1440-I22)</f>
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>57</v>
@@ -1914,7 +1914,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F25" s="9">
         <v>250</v>
@@ -1923,15 +1923,15 @@
         <v>5</v>
       </c>
       <c r="H25" s="9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I25" s="10">
         <f t="shared" si="6"/>
-        <v>810</v>
+        <v>860</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="7"/>
-        <v>630</v>
+        <v>580</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>49</v>
@@ -1955,10 +1955,10 @@
         <v>80</v>
       </c>
       <c r="D26" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E26" s="9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F26" s="9">
         <v>200</v>
@@ -1967,15 +1967,15 @@
         <v>4</v>
       </c>
       <c r="H26" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I26" s="10">
         <f t="shared" si="6"/>
-        <v>640</v>
+        <v>920</v>
       </c>
       <c r="J26" s="10">
         <f t="shared" si="7"/>
-        <v>800</v>
+        <v>520</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>49</v>
@@ -1999,10 +1999,10 @@
         <v>80</v>
       </c>
       <c r="D27" s="9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E27" s="9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F27" s="9">
         <v>250</v>
@@ -2011,15 +2011,15 @@
         <v>5</v>
       </c>
       <c r="H27" s="9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I27" s="10">
         <f t="shared" si="6"/>
-        <v>690</v>
+        <v>870</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="7"/>
-        <v>750</v>
+        <v>570</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>56</v>
@@ -2043,10 +2043,10 @@
         <v>80</v>
       </c>
       <c r="D28" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E28" s="9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F28" s="9">
         <v>300</v>
@@ -2059,11 +2059,11 @@
       </c>
       <c r="I28" s="10">
         <f t="shared" si="6"/>
-        <v>720</v>
+        <v>990</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="7"/>
-        <v>720</v>
+        <v>450</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>49</v>
@@ -2087,10 +2087,10 @@
         <v>120</v>
       </c>
       <c r="D29" s="9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="E29" s="9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F29" s="9">
         <v>0</v>
@@ -2099,15 +2099,15 @@
         <v>0</v>
       </c>
       <c r="H29" s="9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="I29" s="10">
         <f t="shared" si="6"/>
-        <v>540</v>
+        <v>960</v>
       </c>
       <c r="J29" s="10">
         <f t="shared" si="7"/>
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>60</v>
@@ -2131,10 +2131,10 @@
         <v>10</v>
       </c>
       <c r="D30" s="9">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="E30" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F30" s="9">
         <v>0</v>
@@ -2143,15 +2143,15 @@
         <v>0</v>
       </c>
       <c r="H30" s="9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I30" s="10">
         <f t="shared" si="6"/>
-        <v>450</v>
+        <v>970</v>
       </c>
       <c r="J30" s="10">
         <f t="shared" si="7"/>
-        <v>990</v>
+        <v>470</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>49</v>
@@ -2175,10 +2175,10 @@
         <v>80</v>
       </c>
       <c r="D31" s="9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E31" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F31" s="9">
         <v>350</v>
@@ -2187,15 +2187,15 @@
         <v>7</v>
       </c>
       <c r="H31" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I31" s="10">
         <f t="shared" si="6"/>
-        <v>840</v>
+        <v>1000</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="7"/>
-        <v>600</v>
+        <v>440</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>49</v>
@@ -2219,10 +2219,10 @@
         <v>80</v>
       </c>
       <c r="D32" s="9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E32" s="9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F32" s="9">
         <v>250</v>
@@ -2231,15 +2231,15 @@
         <v>5</v>
       </c>
       <c r="H32" s="9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I32" s="10">
         <f t="shared" si="6"/>
-        <v>670</v>
+        <v>930</v>
       </c>
       <c r="J32" s="10">
         <f t="shared" si="7"/>
-        <v>770</v>
+        <v>510</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>49</v>
@@ -2263,10 +2263,10 @@
         <v>80</v>
       </c>
       <c r="D33" s="9">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E33" s="9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33" s="9">
         <v>200</v>
@@ -2275,15 +2275,15 @@
         <v>4</v>
       </c>
       <c r="H33" s="9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I33" s="10">
         <f t="shared" si="6"/>
-        <v>700</v>
+        <v>1060</v>
       </c>
       <c r="J33" s="10">
         <f t="shared" si="7"/>
-        <v>740</v>
+        <v>380</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>56</v>
@@ -2411,15 +2411,15 @@
         <v>0</v>
       </c>
       <c r="H36" s="9">
-        <v>150</v>
+        <v>360</v>
       </c>
       <c r="I36" s="10">
         <f t="shared" si="6"/>
-        <v>480</v>
+        <v>690</v>
       </c>
       <c r="J36" s="10">
         <f t="shared" si="7"/>
-        <v>960</v>
+        <v>750</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>60</v>
@@ -2457,15 +2457,15 @@
         <v>0</v>
       </c>
       <c r="H37" s="9">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="I37" s="10">
         <f t="shared" si="6"/>
-        <v>520</v>
+        <v>910</v>
       </c>
       <c r="J37" s="10">
         <f t="shared" si="7"/>
-        <v>920</v>
+        <v>530</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>49</v>
@@ -2632,7 +2632,7 @@
         <v>120</v>
       </c>
       <c r="E41" s="9">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F41" s="9">
         <v>250</v>
@@ -2645,11 +2645,11 @@
       </c>
       <c r="I41" s="10">
         <f t="shared" si="6"/>
-        <v>790</v>
+        <v>850</v>
       </c>
       <c r="J41" s="10">
         <f t="shared" si="7"/>
-        <v>650</v>
+        <v>590</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>56</v>
@@ -2903,7 +2903,7 @@
         <v>80</v>
       </c>
       <c r="D47" s="9">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="E47" s="9">
         <v>60</v>
@@ -2919,11 +2919,11 @@
       </c>
       <c r="I47" s="10">
         <f t="shared" si="6"/>
-        <v>980</v>
+        <v>940</v>
       </c>
       <c r="J47" s="10">
         <f t="shared" si="7"/>
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>56</v>
@@ -2949,7 +2949,7 @@
         <v>80</v>
       </c>
       <c r="D48" s="9">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E48" s="9">
         <v>30</v>
@@ -2965,11 +2965,11 @@
       </c>
       <c r="I48" s="10">
         <f t="shared" si="6"/>
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J48" s="10">
         <f t="shared" si="7"/>
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>49</v>
@@ -2994,46 +2994,72 @@
       <c r="C49" s="9">
         <v>80</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
+      <c r="D49" s="9">
+        <v>120</v>
+      </c>
+      <c r="E49" s="9">
+        <v>60</v>
+      </c>
       <c r="F49" s="9">
         <v>300</v>
       </c>
       <c r="G49" s="9">
         <v>6</v>
       </c>
-      <c r="H49" s="9"/>
+      <c r="H49" s="9">
+        <v>60</v>
+      </c>
       <c r="I49" s="10">
         <f t="shared" si="6"/>
-        <v>740</v>
+        <v>980</v>
       </c>
       <c r="J49" s="10">
         <f t="shared" si="7"/>
-        <v>700</v>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
+        <v>460</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="12"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>46291</v>
       </c>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+      <c r="B50" s="9">
+        <v>540</v>
+      </c>
+      <c r="C50" s="9">
+        <v>0</v>
+      </c>
+      <c r="D50" s="9">
+        <v>300</v>
+      </c>
+      <c r="E50" s="9">
+        <v>180</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>40</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="7"/>
-        <v/>
+        <v>380</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="11"/>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0F1F00-EF74-4F56-B43F-C46E180FC0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2765960-686D-4621-8D6F-53B4D492F4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,33 @@
   </si>
   <si>
     <t>Started my daily recording.</t>
+  </si>
+  <si>
+    <t>Focused on completing my pending academic work.</t>
+  </si>
+  <si>
+    <t>Focused on improving my study routine.</t>
+  </si>
+  <si>
+    <t>Reviewed the topics covered in class.</t>
+  </si>
+  <si>
+    <t>Practiced Python and worked on improving my coding skills.</t>
+  </si>
+  <si>
+    <t>Started preparing for my upcoming examination.</t>
+  </si>
+  <si>
+    <t>Had a good and productive day.</t>
+  </si>
+  <si>
+    <t>Played football and enjoyed some time away from academics.</t>
+  </si>
+  <si>
+    <t>Revised the topics I studied recently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After 2 Months I am back to my home. </t>
   </si>
 </sst>
 </file>
@@ -915,7 +942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -1136,7 +1163,9 @@
       <c r="M7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="12"/>
+      <c r="N7" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
@@ -1270,7 +1299,9 @@
       <c r="M10" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="12"/>
+      <c r="N10" s="12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
@@ -1438,7 +1469,7 @@
         <v>460</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L14" s="11" t="s">
         <v>56</v>
@@ -1622,7 +1653,9 @@
       <c r="M18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="12"/>
+      <c r="N18" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
@@ -1788,11 +1821,11 @@
         <v>30</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I52" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" ref="I22:I53" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v>790</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" ref="J22:J52" si="7">IF(I22="","",1440-I22)</f>
+        <f t="shared" ref="J22:J53" si="7">IF(I22="","",1440-I22)</f>
         <v>650</v>
       </c>
       <c r="K22" s="11" t="s">
@@ -2294,7 +2327,9 @@
       <c r="M33" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N33" s="12"/>
+      <c r="N33" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
@@ -2706,7 +2741,9 @@
       <c r="M42" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N42" s="12"/>
+      <c r="N42" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
@@ -3026,7 +3063,9 @@
       <c r="M49" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N49" s="12"/>
+      <c r="N49" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
@@ -3061,58 +3100,226 @@
         <f t="shared" si="7"/>
         <v>380</v>
       </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
+      <c r="K50" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>46292</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+      <c r="B51" s="9">
+        <v>300</v>
+      </c>
+      <c r="C51" s="9">
+        <v>120</v>
+      </c>
+      <c r="D51" s="9">
+        <v>180</v>
+      </c>
+      <c r="E51" s="9">
+        <v>40</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>60</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>700</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
+        <v>740</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>46293</v>
       </c>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+      <c r="B52" s="9">
+        <v>360</v>
+      </c>
+      <c r="C52" s="9">
+        <v>0</v>
+      </c>
+      <c r="D52" s="9">
+        <v>100</v>
+      </c>
+      <c r="E52" s="9">
+        <v>60</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>150</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>670</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
+        <v>770</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N52" s="12"/>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A53" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="9">
+        <v>420</v>
+      </c>
+      <c r="C53" s="9">
+        <v>30</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9">
+        <v>30</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>30</v>
+      </c>
+      <c r="I53" s="10">
+        <f t="shared" si="6"/>
+        <v>510</v>
+      </c>
+      <c r="J53" s="10">
+        <f t="shared" si="7"/>
+        <v>930</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="12"/>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="12"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="12"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3122,26 +3329,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J52">
+  <conditionalFormatting sqref="J6:J57">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K52" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K57" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L52" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L57" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M52" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M57" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2765960-686D-4621-8D6F-53B4D492F4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6A69E-70A7-445E-994E-A223C182A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,7 +310,64 @@
     <t>Revised the topics I studied recently.</t>
   </si>
   <si>
-    <t xml:space="preserve">After 2 Months I am back to my home. </t>
+    <t xml:space="preserve">After 2 Months I am going to my home. </t>
+  </si>
+  <si>
+    <t>spend whole day in train</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enjoyed every moment with my family </t>
+  </si>
+  <si>
+    <t>completed my python minor project</t>
+  </si>
+  <si>
+    <t>Spent the day following my routine and getting some study work done</t>
+  </si>
+  <si>
+    <t>Continued working on academic tasks and kept up eith with the classes</t>
+  </si>
+  <si>
+    <t>Worked on my studies and stayed consistent with my daily routine</t>
+  </si>
+  <si>
+    <t>Had a slower day and focused on completing the important tasks.</t>
+  </si>
+  <si>
+    <t>Continued with my regular studies and academic work.</t>
+  </si>
+  <si>
+    <t>Spent the day balancing studies, routine, and some personal time.</t>
+  </si>
+  <si>
+    <t>Took some time to rest and recover after a tiring week.</t>
+  </si>
+  <si>
+    <t>Got back to my regular routine and focused on my studies.</t>
+  </si>
+  <si>
+    <t>Started the month with a focus on my studies and academic work.</t>
+  </si>
+  <si>
+    <t>Continued my regular study routine and worked on pending tasks.</t>
+  </si>
+  <si>
+    <t>Spent the day keeping up with classes and reviewing my studies.</t>
+  </si>
+  <si>
+    <t>Focused on completing my academic work before the weekend.</t>
+  </si>
+  <si>
+    <t>Had a productive day and stayed consistent with my routine.</t>
+  </si>
+  <si>
+    <t>Used the weekend to relax and prepare for the week ahead.</t>
+  </si>
+  <si>
+    <t>Started the week by getting back into my regular study routine.</t>
+  </si>
+  <si>
+    <t>Continued working on my classes and academic tasks.</t>
   </si>
 </sst>
 </file>
@@ -320,7 +377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,6 +451,12 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -442,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -473,6 +536,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -942,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -1255,7 +1321,9 @@
       <c r="M9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="12"/>
+      <c r="N9" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
@@ -1326,15 +1394,15 @@
         <v>5</v>
       </c>
       <c r="H11" s="9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>49</v>
@@ -1345,7 +1413,9 @@
       <c r="M11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="12"/>
+      <c r="N11" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
@@ -1370,15 +1440,15 @@
         <v>4</v>
       </c>
       <c r="H12" s="9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>49</v>
@@ -1389,7 +1459,9 @@
       <c r="M12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="12"/>
+      <c r="N12" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
@@ -1433,7 +1505,9 @@
       <c r="M13" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="N13" s="12"/>
+      <c r="N13" s="12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
@@ -1458,15 +1532,15 @@
         <v>6</v>
       </c>
       <c r="H14" s="9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I14" s="10">
         <f t="shared" ref="I14:I18" si="2">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v>980</v>
+        <v>1060</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" ref="J14:J18" si="3">IF(I14="","",1440-I14)</f>
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>49</v>
@@ -1477,7 +1551,9 @@
       <c r="M14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="12"/>
+      <c r="N14" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
@@ -1521,7 +1597,9 @@
       <c r="M15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="12"/>
+      <c r="N15" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
@@ -1565,7 +1643,9 @@
       <c r="M16" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="N16" s="12"/>
+      <c r="N16" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
@@ -1609,7 +1689,9 @@
       <c r="M17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N17" s="12"/>
+      <c r="N17" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
@@ -1821,11 +1903,11 @@
         <v>30</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I53" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" ref="I22:I58" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v>790</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" ref="J22:J53" si="7">IF(I22="","",1440-I22)</f>
+        <f t="shared" ref="J22:J58" si="7">IF(I22="","",1440-I22)</f>
         <v>650</v>
       </c>
       <c r="K22" s="11" t="s">
@@ -1975,7 +2057,9 @@
       <c r="M25" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N25" s="12"/>
+      <c r="N25" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
@@ -2019,7 +2103,9 @@
       <c r="M26" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="12"/>
+      <c r="N26" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
@@ -2063,7 +2149,9 @@
       <c r="M27" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N27" s="12"/>
+      <c r="N27" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
@@ -2107,7 +2195,9 @@
       <c r="M28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N28" s="12"/>
+      <c r="N28" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
@@ -2151,7 +2241,9 @@
       <c r="M29" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="N29" s="12"/>
+      <c r="N29" s="12" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
@@ -2195,7 +2287,9 @@
       <c r="M30" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N30" s="12"/>
+      <c r="N30" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
@@ -2239,7 +2333,9 @@
       <c r="M31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="12"/>
+      <c r="N31" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
@@ -2283,7 +2379,9 @@
       <c r="M32" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N32" s="12"/>
+      <c r="N32" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
@@ -3253,73 +3351,263 @@
       <c r="A54" s="8">
         <v>46295</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="12"/>
+      <c r="B54" s="9">
+        <v>450</v>
+      </c>
+      <c r="C54" s="9">
+        <v>0</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>240</v>
+      </c>
+      <c r="I54" s="10">
+        <f t="shared" si="6"/>
+        <v>690</v>
+      </c>
+      <c r="J54" s="10">
+        <f t="shared" si="7"/>
+        <v>750</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>46296</v>
       </c>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
+      <c r="B55" s="9">
+        <v>300</v>
+      </c>
+      <c r="C55" s="9">
+        <v>20</v>
+      </c>
+      <c r="D55" s="9">
+        <v>30</v>
+      </c>
+      <c r="E55" s="9">
+        <v>20</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0</v>
+      </c>
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
+        <v>300</v>
+      </c>
+      <c r="I55" s="10">
+        <f t="shared" si="6"/>
+        <v>670</v>
+      </c>
+      <c r="J55" s="10">
+        <f t="shared" si="7"/>
+        <v>770</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>46297</v>
       </c>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
+      <c r="B56" s="9">
+        <v>540</v>
+      </c>
+      <c r="C56" s="9">
+        <v>30</v>
+      </c>
+      <c r="D56" s="9">
+        <v>60</v>
+      </c>
+      <c r="E56" s="9">
+        <v>30</v>
+      </c>
+      <c r="F56" s="9">
+        <v>0</v>
+      </c>
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
+        <v>120</v>
+      </c>
+      <c r="I56" s="10">
+        <f t="shared" si="6"/>
+        <v>780</v>
+      </c>
+      <c r="J56" s="10">
+        <f t="shared" si="7"/>
+        <v>660</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N56" s="12"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>46298</v>
       </c>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
+      <c r="B57" s="9">
+        <v>420</v>
+      </c>
+      <c r="C57" s="9">
+        <v>30</v>
+      </c>
+      <c r="D57" s="9">
+        <v>80</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0</v>
+      </c>
+      <c r="G57" s="9">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9">
+        <v>260</v>
+      </c>
+      <c r="I57" s="10">
+        <f t="shared" si="6"/>
+        <v>790</v>
+      </c>
+      <c r="J57" s="10">
+        <f t="shared" si="7"/>
+        <v>650</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="N57" s="12"/>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B58" s="9">
+        <v>540</v>
+      </c>
+      <c r="C58" s="9">
+        <v>0</v>
+      </c>
+      <c r="D58" s="9">
+        <v>60</v>
+      </c>
+      <c r="E58" s="9">
+        <v>50</v>
+      </c>
+      <c r="F58" s="9">
+        <v>0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>200</v>
+      </c>
+      <c r="I58" s="10">
+        <f t="shared" si="6"/>
+        <v>850</v>
+      </c>
+      <c r="J58" s="10">
+        <f t="shared" si="7"/>
+        <v>590</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A59" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="12"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3329,21 +3617,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J57">
+  <conditionalFormatting sqref="J6:J60">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K57" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K60" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L57" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L60" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M57" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M60" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6A69E-70A7-445E-994E-A223C182A75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B3F6F7-3BAB-4921-887F-E08D8CF4964D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,15 @@
   </si>
   <si>
     <t>Continued working on my classes and academic tasks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online class started </t>
+  </si>
+  <si>
+    <t>Eat some favourite foods</t>
+  </si>
+  <si>
+    <t>Unfortunately, my routine was disrupted due to some issues at college.</t>
   </si>
 </sst>
 </file>
@@ -532,13 +541,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1049,53 +1058,53 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12625822</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1459,7 +1468,7 @@
       <c r="M12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N12" s="14" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1903,11 +1912,11 @@
         <v>30</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I58" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" ref="I22:I59" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v>790</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" ref="J22:J58" si="7">IF(I22="","",1440-I22)</f>
+        <f t="shared" ref="J22:J59" si="7">IF(I22="","",1440-I22)</f>
         <v>650</v>
       </c>
       <c r="K22" s="11" t="s">
@@ -3299,7 +3308,9 @@
       <c r="M52" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N52" s="12"/>
+      <c r="N52" s="12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
@@ -3481,7 +3492,9 @@
       <c r="M56" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N56" s="12"/>
+      <c r="N56" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
@@ -3525,7 +3538,9 @@
       <c r="M57" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N57" s="12"/>
+      <c r="N57" s="12" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
@@ -3577,24 +3592,50 @@
       <c r="A59" s="8">
         <v>46300</v>
       </c>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
+      <c r="B59" s="9">
+        <v>420</v>
+      </c>
+      <c r="C59" s="9">
+        <v>20</v>
+      </c>
+      <c r="D59" s="9">
+        <v>180</v>
+      </c>
+      <c r="E59" s="9">
+        <v>60</v>
+      </c>
+      <c r="F59" s="9">
+        <v>350</v>
+      </c>
+      <c r="G59" s="9">
+        <v>7</v>
+      </c>
+      <c r="H59" s="9">
+        <v>50</v>
+      </c>
+      <c r="I59" s="10">
+        <f t="shared" si="6"/>
+        <v>1080</v>
+      </c>
+      <c r="J59" s="10">
+        <f t="shared" si="7"/>
+        <v>360</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8">
-        <v>46301</v>
-      </c>
+      <c r="A60" s="8"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B3F6F7-3BAB-4921-887F-E08D8CF4964D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3D3740-D315-4BF4-996E-05EEA7B1AFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1017,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -1031,8 +1031,8 @@
     <col min="9" max="9" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19" customWidth="1"/>
+    <col min="13" max="13" width="8.33203125" customWidth="1"/>
     <col min="14" max="14" width="64.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1164,7 +1164,7 @@
         <v>150</v>
       </c>
       <c r="E6" s="9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F6" s="9">
         <v>250</v>
@@ -1177,11 +1177,11 @@
       </c>
       <c r="I6" s="10">
         <f t="shared" ref="I6:I13" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="J6" s="10">
         <f t="shared" ref="J6:J13" si="1">IF(I6="","",1440-I6)</f>
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>60</v>
@@ -1190,7 +1190,7 @@
         <v>50</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
         <v>82</v>
@@ -1210,7 +1210,7 @@
         <v>120</v>
       </c>
       <c r="E7" s="9">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F7" s="9">
         <v>300</v>
@@ -1223,17 +1223,17 @@
       </c>
       <c r="I7" s="10">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1110</v>
       </c>
       <c r="J7" s="10">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>58</v>
@@ -1256,7 +1256,7 @@
         <v>240</v>
       </c>
       <c r="E8" s="9">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -1269,17 +1269,17 @@
       </c>
       <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1065</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>60</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M8" s="11" t="s">
         <v>58</v>
@@ -1302,7 +1302,7 @@
         <v>300</v>
       </c>
       <c r="E9" s="9">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F9" s="9">
         <v>0</v>
@@ -1315,20 +1315,20 @@
       </c>
       <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1080</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N9" s="12" t="s">
         <v>95</v>
@@ -1348,7 +1348,7 @@
         <v>100</v>
       </c>
       <c r="E10" s="9">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="F10" s="9">
         <v>350</v>
@@ -1361,20 +1361,20 @@
       </c>
       <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1110</v>
       </c>
       <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>50</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N10" s="12" t="s">
         <v>85</v>
@@ -1394,7 +1394,7 @@
         <v>120</v>
       </c>
       <c r="E11" s="9">
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="F11" s="9">
         <v>250</v>
@@ -1407,14 +1407,14 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>915</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>525</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>56</v>
@@ -1460,13 +1460,13 @@
         <v>420</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N12" s="14" t="s">
         <v>97</v>
@@ -1486,7 +1486,7 @@
         <v>120</v>
       </c>
       <c r="E13" s="9">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F13" s="9">
         <v>250</v>
@@ -1499,20 +1499,20 @@
       </c>
       <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L13" s="11" t="s">
         <v>56</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N13" s="12" t="s">
         <v>98</v>
@@ -1532,7 +1532,7 @@
         <v>120</v>
       </c>
       <c r="E14" s="9">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F14" s="9">
         <v>300</v>
@@ -1545,20 +1545,20 @@
       </c>
       <c r="I14" s="10">
         <f t="shared" ref="I14:I18" si="2">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v>1060</v>
+        <v>1090</v>
       </c>
       <c r="J14" s="10">
         <f t="shared" ref="J14:J18" si="3">IF(I14="","",1440-I14)</f>
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N14" s="12" t="s">
         <v>99</v>
@@ -1578,7 +1578,7 @@
         <v>360</v>
       </c>
       <c r="E15" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F15" s="9">
         <v>0</v>
@@ -1591,20 +1591,20 @@
       </c>
       <c r="I15" s="10">
         <f t="shared" si="2"/>
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="J15" s="10">
         <f t="shared" si="3"/>
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N15" s="12" t="s">
         <v>100</v>
@@ -1615,7 +1615,7 @@
         <v>46257</v>
       </c>
       <c r="B16" s="9">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="C16" s="9">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>300</v>
       </c>
       <c r="E16" s="9">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F16" s="9">
         <v>0</v>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="I16" s="10">
         <f t="shared" si="2"/>
-        <v>860</v>
+        <v>670</v>
       </c>
       <c r="J16" s="10">
         <f t="shared" si="3"/>
-        <v>580</v>
+        <v>770</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>57</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M16" s="11" t="s">
         <v>57</v>
@@ -1661,7 +1661,7 @@
         <v>46258</v>
       </c>
       <c r="B17" s="9">
-        <v>360</v>
+        <v>480</v>
       </c>
       <c r="C17" s="9">
         <v>80</v>
@@ -1670,7 +1670,7 @@
         <v>120</v>
       </c>
       <c r="E17" s="9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F17" s="9">
         <v>350</v>
@@ -1683,20 +1683,20 @@
       </c>
       <c r="I17" s="10">
         <f t="shared" si="2"/>
-        <v>980</v>
+        <v>1110</v>
       </c>
       <c r="J17" s="10">
         <f t="shared" si="3"/>
-        <v>460</v>
+        <v>330</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N17" s="12" t="s">
         <v>102</v>
@@ -1707,7 +1707,7 @@
         <v>46259</v>
       </c>
       <c r="B18" s="9">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C18" s="9">
         <v>80</v>
@@ -1729,17 +1729,17 @@
       </c>
       <c r="I18" s="10">
         <f t="shared" si="2"/>
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="J18" s="10">
         <f t="shared" si="3"/>
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M18" s="11" t="s">
         <v>51</v>
@@ -1762,7 +1762,7 @@
         <v>210</v>
       </c>
       <c r="E19" s="9">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F19" s="9">
         <v>200</v>
@@ -1775,20 +1775,20 @@
       </c>
       <c r="I19" s="10">
         <f t="shared" ref="I19:I21" si="4">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
-        <v>840</v>
+        <v>810</v>
       </c>
       <c r="J19" s="10">
         <f t="shared" ref="J19:J21" si="5">IF(I19="","",1440-I19)</f>
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N19" s="12" t="s">
         <v>64</v>
@@ -1808,7 +1808,7 @@
         <v>180</v>
       </c>
       <c r="E20" s="9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F20" s="9">
         <v>250</v>
@@ -1821,17 +1821,17 @@
       </c>
       <c r="I20" s="10">
         <f t="shared" si="4"/>
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="J20" s="10">
         <f t="shared" si="5"/>
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>51</v>
@@ -1845,7 +1845,7 @@
         <v>46262</v>
       </c>
       <c r="B21" s="9">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C21" s="9">
         <v>80</v>
@@ -1854,7 +1854,7 @@
         <v>200</v>
       </c>
       <c r="E21" s="9">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="F21" s="9">
         <v>300</v>
@@ -1867,14 +1867,14 @@
       </c>
       <c r="I21" s="10">
         <f t="shared" si="4"/>
-        <v>1090</v>
+        <v>1210</v>
       </c>
       <c r="J21" s="10">
         <f t="shared" si="5"/>
-        <v>350</v>
+        <v>230</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L21" s="11" t="s">
         <v>50</v>
@@ -1900,7 +1900,7 @@
         <v>260</v>
       </c>
       <c r="E22" s="9">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="F22" s="9">
         <v>0</v>
@@ -1912,18 +1912,18 @@
         <v>30</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I59" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
-        <v>790</v>
+        <f t="shared" ref="I22:I64" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <v>685</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" ref="J22:J59" si="7">IF(I22="","",1440-I22)</f>
-        <v>650</v>
+        <f t="shared" ref="J22:J64" si="7">IF(I22="","",1440-I22)</f>
+        <v>755</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>57</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>57</v>
@@ -1946,7 +1946,7 @@
         <v>240</v>
       </c>
       <c r="E23" s="9">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="F23" s="9">
         <v>0</v>
@@ -1959,20 +1959,20 @@
       </c>
       <c r="I23" s="10">
         <f t="shared" si="6"/>
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="J23" s="10">
         <f>IF(I23="","",1440-I23)</f>
-        <v>640</v>
+        <v>540</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>56</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N23" s="12" t="s">
         <v>67</v>
@@ -1992,7 +1992,7 @@
         <v>150</v>
       </c>
       <c r="E24" s="9">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F24" s="9">
         <v>350</v>
@@ -2005,14 +2005,14 @@
       </c>
       <c r="I24" s="10">
         <f t="shared" si="6"/>
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="J24" s="10">
         <f t="shared" si="7"/>
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L24" s="11" t="s">
         <v>56</v>
@@ -2038,7 +2038,7 @@
         <v>60</v>
       </c>
       <c r="E25" s="9">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F25" s="9">
         <v>250</v>
@@ -2051,17 +2051,17 @@
       </c>
       <c r="I25" s="10">
         <f t="shared" si="6"/>
-        <v>860</v>
+        <v>940</v>
       </c>
       <c r="J25" s="10">
         <f t="shared" si="7"/>
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>58</v>
@@ -2104,10 +2104,10 @@
         <v>520</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>51</v>
@@ -2130,7 +2130,7 @@
         <v>120</v>
       </c>
       <c r="E27" s="9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F27" s="9">
         <v>250</v>
@@ -2143,14 +2143,14 @@
       </c>
       <c r="I27" s="10">
         <f t="shared" si="6"/>
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="7"/>
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L27" s="11" t="s">
         <v>56</v>
@@ -2176,7 +2176,7 @@
         <v>200</v>
       </c>
       <c r="E28" s="9">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F28" s="9">
         <v>300</v>
@@ -2189,17 +2189,17 @@
       </c>
       <c r="I28" s="10">
         <f t="shared" si="6"/>
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="J28" s="10">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>51</v>
@@ -2222,7 +2222,7 @@
         <v>180</v>
       </c>
       <c r="E29" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F29" s="9">
         <v>0</v>
@@ -2235,11 +2235,11 @@
       </c>
       <c r="I29" s="10">
         <f t="shared" si="6"/>
-        <v>960</v>
+        <v>980</v>
       </c>
       <c r="J29" s="10">
         <f t="shared" si="7"/>
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>60</v>
@@ -2268,7 +2268,7 @@
         <v>350</v>
       </c>
       <c r="E30" s="9">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F30" s="9">
         <v>0</v>
@@ -2281,20 +2281,20 @@
       </c>
       <c r="I30" s="10">
         <f t="shared" si="6"/>
-        <v>970</v>
+        <v>1010</v>
       </c>
       <c r="J30" s="10">
         <f t="shared" si="7"/>
-        <v>470</v>
+        <v>430</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N30" s="12" t="s">
         <v>108</v>
@@ -2314,7 +2314,7 @@
         <v>120</v>
       </c>
       <c r="E31" s="9">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F31" s="9">
         <v>350</v>
@@ -2327,17 +2327,17 @@
       </c>
       <c r="I31" s="10">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="J31" s="10">
         <f t="shared" si="7"/>
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M31" s="11" t="s">
         <v>51</v>
@@ -2360,7 +2360,7 @@
         <v>120</v>
       </c>
       <c r="E32" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F32" s="9">
         <v>250</v>
@@ -2373,17 +2373,17 @@
       </c>
       <c r="I32" s="10">
         <f t="shared" si="6"/>
-        <v>930</v>
+        <v>910</v>
       </c>
       <c r="J32" s="10">
         <f t="shared" si="7"/>
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M32" s="11" t="s">
         <v>51</v>
@@ -2406,7 +2406,7 @@
         <v>200</v>
       </c>
       <c r="E33" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F33" s="9">
         <v>200</v>
@@ -2419,20 +2419,20 @@
       </c>
       <c r="I33" s="10">
         <f t="shared" si="6"/>
-        <v>1060</v>
+        <v>1080</v>
       </c>
       <c r="J33" s="10">
         <f t="shared" si="7"/>
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N33" s="12" t="s">
         <v>86</v>
@@ -2452,7 +2452,7 @@
         <v>150</v>
       </c>
       <c r="E34" s="9">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F34" s="9">
         <v>250</v>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="I34" s="10">
         <f t="shared" si="6"/>
-        <v>980</v>
+        <v>950</v>
       </c>
       <c r="J34" s="10">
         <f t="shared" si="7"/>
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M34" s="11" t="s">
         <v>51</v>
@@ -2498,7 +2498,7 @@
         <v>120</v>
       </c>
       <c r="E35" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F35" s="9">
         <v>300</v>
@@ -2511,14 +2511,14 @@
       </c>
       <c r="I35" s="10">
         <f t="shared" si="6"/>
-        <v>990</v>
+        <v>1010</v>
       </c>
       <c r="J35" s="10">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L35" s="11" t="s">
         <v>50</v>
@@ -2567,7 +2567,7 @@
         <v>60</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="M36" s="11" t="s">
         <v>58</v>
@@ -2610,7 +2610,7 @@
         <v>530</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L37" s="11" t="s">
         <v>50</v>
@@ -2636,7 +2636,7 @@
         <v>180</v>
       </c>
       <c r="E38" s="9">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F38" s="9">
         <v>350</v>
@@ -2649,17 +2649,17 @@
       </c>
       <c r="I38" s="10">
         <f t="shared" si="6"/>
-        <v>1030</v>
+        <v>1000</v>
       </c>
       <c r="J38" s="10">
         <f t="shared" si="7"/>
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M38" s="11" t="s">
         <v>57</v>
@@ -2682,7 +2682,7 @@
         <v>180</v>
       </c>
       <c r="E39" s="9">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F39" s="9">
         <v>250</v>
@@ -2695,17 +2695,17 @@
       </c>
       <c r="I39" s="10">
         <f t="shared" si="6"/>
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J39" s="10">
         <f t="shared" si="7"/>
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M39" s="11" t="s">
         <v>51</v>
@@ -2728,7 +2728,7 @@
         <v>210</v>
       </c>
       <c r="E40" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F40" s="9">
         <v>250</v>
@@ -2741,14 +2741,14 @@
       </c>
       <c r="I40" s="10">
         <f t="shared" si="6"/>
-        <v>1040</v>
+        <v>1060</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="7"/>
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L40" s="11" t="s">
         <v>50</v>
@@ -2794,7 +2794,7 @@
         <v>590</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>56</v>
@@ -2820,7 +2820,7 @@
         <v>170</v>
       </c>
       <c r="E42" s="9">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="F42" s="9">
         <v>300</v>
@@ -2833,14 +2833,14 @@
       </c>
       <c r="I42" s="10">
         <f t="shared" si="6"/>
-        <v>1050</v>
+        <v>1160</v>
       </c>
       <c r="J42" s="10">
         <f t="shared" si="7"/>
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L42" s="11" t="s">
         <v>50</v>
@@ -2866,7 +2866,7 @@
         <v>180</v>
       </c>
       <c r="E43" s="9">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F43" s="9">
         <v>60</v>
@@ -2879,17 +2879,17 @@
       </c>
       <c r="I43" s="10">
         <f t="shared" si="6"/>
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="J43" s="10">
         <f t="shared" si="7"/>
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>56</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="M43" s="11" t="s">
         <v>51</v>
@@ -2912,7 +2912,7 @@
         <v>180</v>
       </c>
       <c r="E44" s="9">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F44" s="9">
         <v>0</v>
@@ -2925,20 +2925,20 @@
       </c>
       <c r="I44" s="10">
         <f t="shared" si="6"/>
-        <v>880</v>
+        <v>970</v>
       </c>
       <c r="J44" s="10">
         <f t="shared" si="7"/>
-        <v>560</v>
+        <v>470</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L44" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M44" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N44" s="12" t="s">
         <v>77</v>
@@ -2981,7 +2981,7 @@
         <v>49</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M45" s="11" t="s">
         <v>51</v>
@@ -3030,7 +3030,7 @@
         <v>59</v>
       </c>
       <c r="M46" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N46" s="12" t="s">
         <v>78</v>
@@ -3053,7 +3053,7 @@
         <v>60</v>
       </c>
       <c r="F47" s="9">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="G47" s="9">
         <v>4</v>
@@ -3063,11 +3063,11 @@
       </c>
       <c r="I47" s="10">
         <f t="shared" si="6"/>
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="J47" s="10">
         <f t="shared" si="7"/>
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>56</v>
@@ -3076,7 +3076,7 @@
         <v>56</v>
       </c>
       <c r="M47" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N47" s="12" t="s">
         <v>70</v>
@@ -3116,13 +3116,13 @@
         <v>440</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L48" s="11" t="s">
         <v>56</v>
       </c>
       <c r="M48" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N48" s="12" t="s">
         <v>80</v>
@@ -3162,7 +3162,7 @@
         <v>460</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L49" s="11" t="s">
         <v>50</v>
@@ -3303,7 +3303,7 @@
         <v>56</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="M52" s="11" t="s">
         <v>51</v>
@@ -3349,10 +3349,10 @@
         <v>49</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N53" s="12" t="s">
         <v>91</v>
@@ -3395,7 +3395,7 @@
         <v>49</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="M54" s="11" t="s">
         <v>58</v>
@@ -3444,7 +3444,7 @@
         <v>61</v>
       </c>
       <c r="M55" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N55" s="12" t="s">
         <v>93</v>
@@ -3490,7 +3490,7 @@
         <v>50</v>
       </c>
       <c r="M56" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N56" s="12" t="s">
         <v>87</v>
@@ -3530,13 +3530,13 @@
         <v>650</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="L57" s="11" t="s">
         <v>50</v>
       </c>
       <c r="M57" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N57" s="12" t="s">
         <v>112</v>
@@ -3582,7 +3582,7 @@
         <v>56</v>
       </c>
       <c r="M58" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N58" s="12" t="s">
         <v>94</v>
@@ -3622,33 +3622,291 @@
         <v>360</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M59" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N59" s="12" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
+      <c r="A60" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B60" s="9">
+        <v>540</v>
+      </c>
+      <c r="C60" s="9">
+        <v>20</v>
+      </c>
+      <c r="D60" s="9">
+        <v>100</v>
+      </c>
+      <c r="E60" s="9">
+        <v>120</v>
+      </c>
+      <c r="F60" s="9">
+        <v>250</v>
+      </c>
+      <c r="G60" s="9">
+        <v>5</v>
+      </c>
+      <c r="H60" s="9">
+        <v>90</v>
+      </c>
+      <c r="I60" s="10">
+        <f t="shared" si="6"/>
+        <v>1120</v>
+      </c>
+      <c r="J60" s="10">
+        <f t="shared" si="7"/>
+        <v>320</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N60" s="12"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B61" s="9">
+        <v>540</v>
+      </c>
+      <c r="C61" s="9">
+        <v>50</v>
+      </c>
+      <c r="D61" s="9">
+        <v>60</v>
+      </c>
+      <c r="E61" s="9">
+        <v>50</v>
+      </c>
+      <c r="F61" s="9">
+        <v>200</v>
+      </c>
+      <c r="G61" s="9">
+        <v>4</v>
+      </c>
+      <c r="H61" s="9">
+        <v>80</v>
+      </c>
+      <c r="I61" s="10">
+        <f t="shared" si="6"/>
+        <v>980</v>
+      </c>
+      <c r="J61" s="10">
+        <f t="shared" si="7"/>
+        <v>460</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N61" s="12"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B62" s="9">
+        <v>420</v>
+      </c>
+      <c r="C62" s="9">
+        <v>10</v>
+      </c>
+      <c r="D62" s="9">
+        <v>80</v>
+      </c>
+      <c r="E62" s="9">
+        <v>30</v>
+      </c>
+      <c r="F62" s="9">
+        <v>250</v>
+      </c>
+      <c r="G62" s="9">
+        <v>5</v>
+      </c>
+      <c r="H62" s="9">
+        <v>120</v>
+      </c>
+      <c r="I62" s="10">
+        <f t="shared" si="6"/>
+        <v>910</v>
+      </c>
+      <c r="J62" s="10">
+        <f t="shared" si="7"/>
+        <v>530</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N62" s="12"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B63" s="9">
+        <v>540</v>
+      </c>
+      <c r="C63" s="9">
+        <v>20</v>
+      </c>
+      <c r="D63" s="9">
+        <v>180</v>
+      </c>
+      <c r="E63" s="9">
+        <v>60</v>
+      </c>
+      <c r="F63" s="9">
+        <v>100</v>
+      </c>
+      <c r="G63" s="9">
+        <v>2</v>
+      </c>
+      <c r="H63" s="9">
+        <v>150</v>
+      </c>
+      <c r="I63" s="10">
+        <f t="shared" si="6"/>
+        <v>1050</v>
+      </c>
+      <c r="J63" s="10">
+        <f t="shared" si="7"/>
+        <v>390</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N63" s="12"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B64" s="9">
+        <v>540</v>
+      </c>
+      <c r="C64" s="9">
+        <v>20</v>
+      </c>
+      <c r="D64" s="9">
+        <v>120</v>
+      </c>
+      <c r="E64" s="9">
+        <v>50</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>200</v>
+      </c>
+      <c r="I64" s="10">
+        <f t="shared" si="6"/>
+        <v>930</v>
+      </c>
+      <c r="J64" s="10">
+        <f t="shared" si="7"/>
+        <v>510</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N64" s="12"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="12"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="10"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="11"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="12"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
+      <c r="K67" s="11"/>
+      <c r="L67" s="11"/>
+      <c r="M67" s="11"/>
+      <c r="N67" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3658,21 +3916,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J60">
+  <conditionalFormatting sqref="J6:J67">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K60" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K67" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L60" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L67" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M60" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M67" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12625822.xlsx
+++ b/12625822.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LPU\sem 1\Python\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3D3740-D315-4BF4-996E-05EEA7B1AFE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4392C30F-75C3-4C96-B85E-8EDD7189848C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1912,11 +1912,11 @@
         <v>30</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" ref="I22:I64" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" ref="I22:I65" si="6">IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
         <v>685</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" ref="J22:J64" si="7">IF(I22="","",1440-I22)</f>
+        <f t="shared" ref="J22:J65" si="7">IF(I22="","",1440-I22)</f>
         <v>755</v>
       </c>
       <c r="K22" s="11" t="s">
@@ -3858,26 +3858,56 @@
       <c r="A65" s="8">
         <v>46306</v>
       </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
+      <c r="B65" s="9">
+        <v>540</v>
+      </c>
+      <c r="C65" s="9">
+        <v>30</v>
+      </c>
+      <c r="D65" s="9">
+        <v>150</v>
+      </c>
+      <c r="E65" s="9">
+        <v>60</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>120</v>
+      </c>
+      <c r="I65" s="10">
+        <f t="shared" si="6"/>
+        <v>900</v>
+      </c>
+      <c r="J65" s="10">
+        <f t="shared" si="7"/>
+        <v>540</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>58</v>
+      </c>
       <c r="N65" s="12"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>46307</v>
       </c>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
+      <c r="B66" s="9">
+        <v>360</v>
+      </c>
+      <c r="C66" s="9">
+        <v>20</v>
+      </c>
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9"/>
